--- a/PROYECTO_ING_SOFT_PROTOTIPO_SISTEMA_VETERINARIO.xlsx
+++ b/PROYECTO_ING_SOFT_PROTOTIPO_SISTEMA_VETERINARIO.xlsx
@@ -5,21 +5,23 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/77756be7ce1b6032/Escritorio/ESTUDIOS/AGRARIA/SEGUNDO SEMESTRE/OFIMATICA DOS/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\genes\Downloads\SISTEMA-DE-AGENDAMIENTO-E-INFORMACI-N-DE-CITAS-PARA-LA-VETERINARIA-MONDELVET\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="8_{35B06F44-8AFB-484E-BDC3-40E30D571348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88928BDE-239D-4C43-9C32-1720425D62C9}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D202D7D1-0D24-458E-9CAA-241E180F2930}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{3AB8A230-48A4-473C-8D8D-C4BAF777D56F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{3AB8A230-48A4-473C-8D8D-C4BAF777D56F}"/>
   </bookViews>
   <sheets>
     <sheet name="Menu Principal" sheetId="6" r:id="rId1"/>
-    <sheet name="Factura" sheetId="5" r:id="rId2"/>
-    <sheet name="Clientes" sheetId="3" r:id="rId3"/>
-    <sheet name="Proveedor" sheetId="4" r:id="rId4"/>
-    <sheet name="Lista de control" sheetId="2" r:id="rId5"/>
+    <sheet name="Calendario" sheetId="7" r:id="rId2"/>
+    <sheet name="Registro de agenda" sheetId="8" r:id="rId3"/>
+    <sheet name="Factura" sheetId="5" r:id="rId4"/>
+    <sheet name="Clientes" sheetId="3" r:id="rId5"/>
+    <sheet name="Proveedor" sheetId="4" r:id="rId6"/>
+    <sheet name="Lista de control" sheetId="2" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -29,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="184">
   <si>
     <t>Codigo</t>
   </si>
@@ -490,16 +492,97 @@
     <t>Servicio/Producto</t>
   </si>
   <si>
-    <t>Limpiar</t>
-  </si>
-  <si>
-    <t>Guardar</t>
-  </si>
-  <si>
     <t>Ruc:</t>
   </si>
   <si>
     <t>Insumos que provee:</t>
+  </si>
+  <si>
+    <t>Año</t>
+  </si>
+  <si>
+    <t>Mes</t>
+  </si>
+  <si>
+    <t>julio</t>
+  </si>
+  <si>
+    <t>Seleccione dia:</t>
+  </si>
+  <si>
+    <t>HORA</t>
+  </si>
+  <si>
+    <t>PACIENTE</t>
+  </si>
+  <si>
+    <t>Lunes</t>
+  </si>
+  <si>
+    <t>Martes</t>
+  </si>
+  <si>
+    <t>Miercoles</t>
+  </si>
+  <si>
+    <t>Jueves</t>
+  </si>
+  <si>
+    <t>Viernes</t>
+  </si>
+  <si>
+    <t>Sabado</t>
+  </si>
+  <si>
+    <t>Domingo</t>
+  </si>
+  <si>
+    <t>BAÑO FELINO</t>
+  </si>
+  <si>
+    <t>FECHA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HORA </t>
+  </si>
+  <si>
+    <t>CONSULTA / SERVICIO</t>
+  </si>
+  <si>
+    <t>Fecha de cita:</t>
+  </si>
+  <si>
+    <t>Hora</t>
+  </si>
+  <si>
+    <t>Paciente</t>
+  </si>
+  <si>
+    <t>Consulta/Servicio:</t>
+  </si>
+  <si>
+    <t>Tutor</t>
+  </si>
+  <si>
+    <t>Contacto:</t>
+  </si>
+  <si>
+    <t>CONTACTO</t>
+  </si>
+  <si>
+    <t>INGRESO DE DATOS DEL PROVEEDOR</t>
+  </si>
+  <si>
+    <t>INGRESO DE PACIENTE PARA AGENDA</t>
+  </si>
+  <si>
+    <t>EDITAR</t>
+  </si>
+  <si>
+    <t>BUSCAR</t>
+  </si>
+  <si>
+    <t>CALENDARIO</t>
   </si>
 </sst>
 </file>
@@ -509,7 +592,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_ &quot;$&quot;* #,##0.00_ ;_ &quot;$&quot;* \-#,##0.00_ ;_ &quot;$&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -644,8 +727,24 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -724,8 +823,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="19">
+  <borders count="27">
     <border>
       <left/>
       <right/>
@@ -935,6 +1040,126 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -942,7 +1167,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="116">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -1024,13 +1249,93 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="9" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="20" fontId="0" fillId="8" borderId="22" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="23" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1042,26 +1347,34 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1070,8 +1383,11 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1085,59 +1401,13 @@
     <xf numFmtId="0" fontId="14" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="9" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="3" builtinId="8"/>
@@ -1145,50 +1415,53 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentaje" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="22">
+  <dxfs count="29">
     <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Bookman Old Style"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
+      <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Bodoni MT"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1294,52 +1567,105 @@
       </fill>
     </dxf>
     <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Bookman Old Style"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Bodoni MT"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2001,6 +2327,288 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>309458</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>146074</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>538634</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>49670</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="Rectángulo: esquinas superiores redondeadas 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A96AFA47-B9E2-419D-B57D-05FB72BFD1CB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5715539" y="3475533"/>
+          <a:ext cx="1756609" cy="1525421"/>
+        </a:xfrm>
+        <a:prstGeom prst="round2SameRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="b"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="es-EC" sz="1600"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="es-EC" sz="1600"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="es-EC" sz="1600"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="es-EC" sz="1600"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="es-EC" sz="1600"/>
+            <a:t>Agendar</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="es-EC" sz="1600" baseline="0"/>
+            <a:t> cita</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-EC" sz="1600"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>281657</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>118270</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>510833</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>21867</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="Rectángulo: esquinas superiores redondeadas 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{82D72525-2F31-4D25-906C-FB3780ADFFE9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5687738" y="744689"/>
+          <a:ext cx="1756609" cy="1525421"/>
+        </a:xfrm>
+        <a:prstGeom prst="round2SameRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="b"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="es-EC" sz="1600"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="es-EC" sz="1600"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="es-EC" sz="1600"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="es-EC" sz="1600"/>
+            <a:t>Citas</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="es-EC" sz="1600" baseline="0"/>
+            <a:t> diarias programadas</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-EC" sz="1600"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>712229</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>154459</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>94391</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>171620</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Imagen 7" descr="agenda vector sólido icono diseño ilustración. hora administración símbolo en blanco antecedentes eps 10 archivo 24028646 Vector en Vecteezy">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5B74D093-F24D-2FC8-6F70-DD79D9918DAA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect l="13851" r="10680" b="22071"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="6118310" y="3664121"/>
+          <a:ext cx="909595" cy="918175"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>178707</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>163041</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>13473</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Imagen 9" descr="469.000+ Agenda Ilustraciones de Stock, gráficos vectoriales libres de derechos y clip art - iStock">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1797803D-B216-4023-EA24-08106E97A227}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect l="7345" t="12513" r="54754" b="13286"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="6169798" y="805126"/>
+          <a:ext cx="926757" cy="915982"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -2053,18 +2661,32 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{6709D95A-2F81-48F6-9E53-E6FC4E714F30}" name="factura" displayName="factura" ref="C15:G25" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{91C00111-3D57-4CCA-AAC9-423164940412}" name="Tabla1" displayName="Tabla1" ref="A1:E58" totalsRowShown="0" headerRowDxfId="28" dataDxfId="27">
+  <autoFilter ref="A1:E58" xr:uid="{91C00111-3D57-4CCA-AAC9-423164940412}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{39CF055C-6203-4E60-A39F-477E7B108B15}" name="FECHA" dataDxfId="26"/>
+    <tableColumn id="2" xr3:uid="{D1FDCB89-07BE-45BB-82BB-9B6725830590}" name="HORA " dataDxfId="25"/>
+    <tableColumn id="3" xr3:uid="{861EC1A6-E285-418D-B2D8-BEFBE46CCD9F}" name="PACIENTE" dataDxfId="24"/>
+    <tableColumn id="4" xr3:uid="{CBC1AAF1-B22D-4632-98D4-DC6BC545C44A}" name="CONSULTA / SERVICIO" dataDxfId="23"/>
+    <tableColumn id="5" xr3:uid="{ACF1A8D0-8064-4808-90C9-B1D45EE34D51}" name="CONTACTO" dataDxfId="22"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{6709D95A-2F81-48F6-9E53-E6FC4E714F30}" name="factura" displayName="factura" ref="C15:G25" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
   <autoFilter ref="C15:G25" xr:uid="{6709D95A-2F81-48F6-9E53-E6FC4E714F30}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{5389A49D-B2BD-4433-BFCA-CE488AE8E797}" name="Codigo" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{72BBC78A-10E2-4CB4-AEC7-9E19106CBF8A}" name="Detalle" dataDxfId="5">
+    <tableColumn id="1" xr3:uid="{5389A49D-B2BD-4433-BFCA-CE488AE8E797}" name="Codigo" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{72BBC78A-10E2-4CB4-AEC7-9E19106CBF8A}" name="Detalle" dataDxfId="18">
       <calculatedColumnFormula>IFERROR(VLOOKUP(factura[[#This Row],[Codigo]],Servicios_Vet[],2,FALSE),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{080B5D02-5895-4073-B46C-9876958E402A}" name="Precio Unit" dataDxfId="4" dataCellStyle="Moneda">
+    <tableColumn id="3" xr3:uid="{080B5D02-5895-4073-B46C-9876958E402A}" name="Precio Unit" dataDxfId="17" dataCellStyle="Moneda">
       <calculatedColumnFormula>IFERROR(VLOOKUP(factura[[#This Row],[Codigo]],Servicios_Vet[],3,FALSE),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{E5448962-5D7B-4C80-BA5C-1A324AC3BAD5}" name="Cant." dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{A561AD75-B839-4E82-BD88-D775A2BAAAD5}" name="Total" dataDxfId="2" dataCellStyle="Moneda">
+    <tableColumn id="4" xr3:uid="{E5448962-5D7B-4C80-BA5C-1A324AC3BAD5}" name="Cant." dataDxfId="16"/>
+    <tableColumn id="5" xr3:uid="{A561AD75-B839-4E82-BD88-D775A2BAAAD5}" name="Total" dataDxfId="15" dataCellStyle="Moneda">
       <calculatedColumnFormula>IFERROR(factura[[#This Row],[Precio Unit]]*factura[[#This Row],[Cant.]]," ")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2072,39 +2694,39 @@
 </table>
 </file>
 
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9B9C92E2-FF0F-484E-8231-ABA5BBE5819E}" name="Clientes" displayName="Clientes" ref="A2:E12" totalsRowShown="0" headerRowDxfId="12">
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9B9C92E2-FF0F-484E-8231-ABA5BBE5819E}" name="Clientes" displayName="Clientes" ref="A2:E12" totalsRowShown="0" headerRowDxfId="14">
   <autoFilter ref="A2:E12" xr:uid="{9B9C92E2-FF0F-484E-8231-ABA5BBE5819E}"/>
   <tableColumns count="5">
-    <tableColumn id="2" xr3:uid="{E6D07DE4-9B6C-47B2-B9E7-A0AE8AFE8584}" name="Cedula" dataDxfId="11"/>
-    <tableColumn id="1" xr3:uid="{441C18B8-5AEE-46B8-8C2A-4AC9E9E4FC85}" name="Nombres" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{774686EC-60F7-4F22-843C-A61B0CB0DEA6}" name="Telefono" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{4468BFD3-A771-4181-B23A-FF2EB8B476AA}" name="Direccion" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{37F7BB74-28E8-4BFC-8B0E-4E9DC9670661}" name="correo electronico" dataDxfId="7" dataCellStyle="Hipervínculo"/>
+    <tableColumn id="2" xr3:uid="{E6D07DE4-9B6C-47B2-B9E7-A0AE8AFE8584}" name="Cedula" dataDxfId="13"/>
+    <tableColumn id="1" xr3:uid="{441C18B8-5AEE-46B8-8C2A-4AC9E9E4FC85}" name="Nombres" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{774686EC-60F7-4F22-843C-A61B0CB0DEA6}" name="Telefono" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{4468BFD3-A771-4181-B23A-FF2EB8B476AA}" name="Direccion" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{37F7BB74-28E8-4BFC-8B0E-4E9DC9670661}" name="correo electronico" dataDxfId="9" dataCellStyle="Hipervínculo"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{8CF7F707-E3DE-4EF9-AFAB-1F6C2488AA35}" name="Proveedores" displayName="Proveedores" ref="A2:D9" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{8CF7F707-E3DE-4EF9-AFAB-1F6C2488AA35}" name="Proveedores" displayName="Proveedores" ref="A2:D9" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
   <autoFilter ref="A2:D9" xr:uid="{8CF7F707-E3DE-4EF9-AFAB-1F6C2488AA35}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{7F365C2A-B46D-4DFA-8C20-CE8F7C8F09EE}" name="Nombre" dataDxfId="19"/>
-    <tableColumn id="2" xr3:uid="{CBF9F121-CFD7-445F-99E7-98001E0BF7AC}" name="Telefono" dataDxfId="18"/>
-    <tableColumn id="3" xr3:uid="{46791C53-B4E9-4A1B-99FB-1BB17B9707F8}" name="Ruc" dataDxfId="17"/>
-    <tableColumn id="4" xr3:uid="{4B3F9DB8-C5F9-4D8B-8FD0-6A7668E4E990}" name="Descripcion_Proveedor" dataDxfId="16"/>
+    <tableColumn id="1" xr3:uid="{7F365C2A-B46D-4DFA-8C20-CE8F7C8F09EE}" name="Nombre" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{CBF9F121-CFD7-445F-99E7-98001E0BF7AC}" name="Telefono" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{46791C53-B4E9-4A1B-99FB-1BB17B9707F8}" name="Ruc" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{4B3F9DB8-C5F9-4D8B-8FD0-6A7668E4E990}" name="Descripcion_Proveedor" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{82E53B18-C482-4919-9B9C-36CA1D660AD9}" name="Servicios_Vet" displayName="Servicios_Vet" ref="A2:E14" totalsRowShown="0" headerRowDxfId="15">
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{82E53B18-C482-4919-9B9C-36CA1D660AD9}" name="Servicios_Vet" displayName="Servicios_Vet" ref="A2:E14" totalsRowShown="0" headerRowDxfId="2">
   <autoFilter ref="A2:E14" xr:uid="{82E53B18-C482-4919-9B9C-36CA1D660AD9}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{3050F31C-5572-42F5-98F3-BA6003A430A0}" name="Codigo" dataDxfId="14"/>
-    <tableColumn id="2" xr3:uid="{2013AF36-48BB-4590-820B-E6973EF5027C}" name="Servicio" dataDxfId="13"/>
+    <tableColumn id="1" xr3:uid="{3050F31C-5572-42F5-98F3-BA6003A430A0}" name="Codigo" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{2013AF36-48BB-4590-820B-E6973EF5027C}" name="Servicio" dataDxfId="0"/>
     <tableColumn id="3" xr3:uid="{47F670A4-0E3D-4029-877A-CB8C36149E0F}" name="Costo" dataCellStyle="Moneda"/>
     <tableColumn id="4" xr3:uid="{03DA183E-9B82-459C-8D2A-4EE1F8C1FFFD}" name="PVP" dataCellStyle="Moneda">
       <calculatedColumnFormula>Servicios_Vet[[#This Row],[Costo]]-(Servicios_Vet[[#This Row],[Costo]]*Servicios_Vet[[#This Row],[Descuento]])</calculatedColumnFormula>
@@ -2412,956 +3034,703 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87B8CAAC-1786-4556-8517-DE778D99C9C9}">
-  <dimension ref="A1:U41"/>
+  <dimension ref="A1:U30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="5" max="5" width="22.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A1" s="65"/>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="66"/>
-      <c r="H1" s="66"/>
-      <c r="I1" s="66"/>
-      <c r="J1" s="66"/>
-      <c r="K1" s="66"/>
-      <c r="L1" s="66"/>
-      <c r="M1" s="66"/>
-      <c r="N1" s="66"/>
-      <c r="O1" s="66"/>
-      <c r="P1" s="66"/>
-      <c r="Q1" s="66"/>
-      <c r="R1" s="66"/>
-      <c r="S1" s="66"/>
-      <c r="T1" s="66"/>
-      <c r="U1" s="67"/>
+      <c r="A1" s="44"/>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="45"/>
+      <c r="K1" s="45"/>
+      <c r="L1" s="45"/>
+      <c r="M1" s="45"/>
+      <c r="N1" s="45"/>
+      <c r="O1" s="45"/>
+      <c r="P1" s="45"/>
+      <c r="Q1" s="45"/>
+      <c r="R1" s="45"/>
+      <c r="S1" s="45"/>
+      <c r="T1" s="45"/>
+      <c r="U1" s="46"/>
     </row>
     <row r="2" spans="1:21" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="68"/>
-      <c r="B2" s="69"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="70" t="s">
+      <c r="A2" s="47"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="79" t="s">
         <v>142</v>
       </c>
-      <c r="G2" s="70"/>
-      <c r="H2" s="70"/>
-      <c r="I2" s="70"/>
-      <c r="J2" s="70"/>
-      <c r="K2" s="70"/>
-      <c r="L2" s="70"/>
-      <c r="M2" s="69"/>
-      <c r="N2" s="69"/>
-      <c r="O2" s="69"/>
-      <c r="P2" s="69"/>
-      <c r="Q2" s="69"/>
-      <c r="R2" s="69"/>
-      <c r="S2" s="69"/>
-      <c r="T2" s="69"/>
-      <c r="U2" s="71"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="79"/>
+      <c r="J2" s="79"/>
+      <c r="K2" s="79"/>
+      <c r="L2" s="79"/>
+      <c r="M2" s="43"/>
+      <c r="N2" s="43"/>
+      <c r="O2" s="43"/>
+      <c r="P2" s="43"/>
+      <c r="Q2" s="43"/>
+      <c r="R2" s="43"/>
+      <c r="S2" s="43"/>
+      <c r="T2" s="43"/>
+      <c r="U2" s="48"/>
     </row>
     <row r="3" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="68"/>
-      <c r="B3" s="69"/>
-      <c r="C3" s="69"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="72"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="70"/>
-      <c r="H3" s="70"/>
-      <c r="I3" s="70"/>
-      <c r="J3" s="70"/>
-      <c r="K3" s="70"/>
-      <c r="L3" s="70"/>
-      <c r="M3" s="69"/>
-      <c r="N3" s="69"/>
-      <c r="O3" s="69"/>
-      <c r="P3" s="69"/>
-      <c r="Q3" s="69"/>
-      <c r="R3" s="69"/>
-      <c r="S3" s="69"/>
-      <c r="T3" s="69"/>
-      <c r="U3" s="71"/>
+      <c r="A3" s="47"/>
+      <c r="B3" s="43"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="79"/>
+      <c r="H3" s="79"/>
+      <c r="I3" s="79"/>
+      <c r="J3" s="79"/>
+      <c r="K3" s="79"/>
+      <c r="L3" s="79"/>
+      <c r="M3" s="43"/>
+      <c r="N3" s="43"/>
+      <c r="O3" s="43"/>
+      <c r="P3" s="43"/>
+      <c r="Q3" s="43"/>
+      <c r="R3" s="43"/>
+      <c r="S3" s="43"/>
+      <c r="T3" s="43"/>
+      <c r="U3" s="48"/>
     </row>
     <row r="4" spans="1:21" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="68"/>
-      <c r="B4" s="69"/>
-      <c r="C4" s="69"/>
-      <c r="D4" s="69"/>
-      <c r="E4" s="72"/>
-      <c r="F4" s="70"/>
-      <c r="G4" s="70"/>
-      <c r="H4" s="70"/>
-      <c r="I4" s="70"/>
-      <c r="J4" s="70"/>
-      <c r="K4" s="70"/>
-      <c r="L4" s="70"/>
-      <c r="M4" s="69"/>
-      <c r="N4" s="69"/>
-      <c r="O4" s="69"/>
-      <c r="P4" s="69"/>
-      <c r="Q4" s="69"/>
-      <c r="R4" s="69"/>
-      <c r="S4" s="69"/>
-      <c r="T4" s="69"/>
-      <c r="U4" s="71"/>
+      <c r="A4" s="47"/>
+      <c r="B4" s="43"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="79"/>
+      <c r="G4" s="79"/>
+      <c r="H4" s="79"/>
+      <c r="I4" s="79"/>
+      <c r="J4" s="79"/>
+      <c r="K4" s="79"/>
+      <c r="L4" s="79"/>
+      <c r="M4" s="43"/>
+      <c r="N4" s="43"/>
+      <c r="O4" s="43"/>
+      <c r="P4" s="43"/>
+      <c r="Q4" s="43"/>
+      <c r="R4" s="43"/>
+      <c r="S4" s="43"/>
+      <c r="T4" s="43"/>
+      <c r="U4" s="48"/>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A5" s="68"/>
-      <c r="B5" s="69"/>
-      <c r="C5" s="69"/>
-      <c r="D5" s="69"/>
-      <c r="E5" s="69"/>
-      <c r="F5" s="69"/>
-      <c r="G5" s="69"/>
-      <c r="H5" s="69"/>
-      <c r="I5" s="69"/>
-      <c r="J5" s="69"/>
-      <c r="K5" s="69"/>
-      <c r="L5" s="69"/>
-      <c r="M5" s="69"/>
-      <c r="N5" s="69"/>
-      <c r="O5" s="69"/>
-      <c r="P5" s="69"/>
-      <c r="Q5" s="69"/>
-      <c r="R5" s="69"/>
-      <c r="S5" s="69"/>
-      <c r="T5" s="69"/>
-      <c r="U5" s="71"/>
+      <c r="A5" s="47"/>
+      <c r="B5" s="43"/>
+      <c r="C5" s="43"/>
+      <c r="D5" s="43"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="43"/>
+      <c r="H5" s="43"/>
+      <c r="I5" s="43"/>
+      <c r="J5" s="43"/>
+      <c r="K5" s="43"/>
+      <c r="L5" s="43"/>
+      <c r="M5" s="43"/>
+      <c r="N5" s="43"/>
+      <c r="O5" s="43"/>
+      <c r="P5" s="43"/>
+      <c r="Q5" s="43"/>
+      <c r="R5" s="43"/>
+      <c r="S5" s="43"/>
+      <c r="T5" s="43"/>
+      <c r="U5" s="48"/>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A6" s="68"/>
-      <c r="B6" s="69"/>
-      <c r="C6" s="69"/>
-      <c r="D6" s="69"/>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69"/>
-      <c r="H6" s="69"/>
-      <c r="I6" s="69"/>
-      <c r="J6" s="69"/>
-      <c r="K6" s="69"/>
-      <c r="L6" s="69"/>
-      <c r="M6" s="69"/>
-      <c r="N6" s="69"/>
-      <c r="O6" s="69"/>
-      <c r="P6" s="69"/>
-      <c r="Q6" s="69"/>
-      <c r="R6" s="69"/>
-      <c r="S6" s="69"/>
-      <c r="T6" s="69"/>
-      <c r="U6" s="71"/>
+      <c r="A6" s="47"/>
+      <c r="B6" s="43"/>
+      <c r="C6" s="43"/>
+      <c r="D6" s="43"/>
+      <c r="E6" s="43"/>
+      <c r="F6" s="43"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="43"/>
+      <c r="I6" s="43"/>
+      <c r="J6" s="43"/>
+      <c r="K6" s="43"/>
+      <c r="L6" s="43"/>
+      <c r="M6" s="43"/>
+      <c r="N6" s="43"/>
+      <c r="O6" s="43"/>
+      <c r="P6" s="43"/>
+      <c r="Q6" s="43"/>
+      <c r="R6" s="43"/>
+      <c r="S6" s="43"/>
+      <c r="T6" s="43"/>
+      <c r="U6" s="48"/>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A7" s="68"/>
-      <c r="B7" s="69"/>
-      <c r="C7" s="69"/>
-      <c r="D7" s="69"/>
-      <c r="E7" s="69"/>
-      <c r="F7" s="69"/>
-      <c r="G7" s="69"/>
-      <c r="H7" s="69"/>
-      <c r="I7" s="69"/>
-      <c r="J7" s="69"/>
-      <c r="K7" s="69"/>
-      <c r="L7" s="69"/>
-      <c r="M7" s="69"/>
-      <c r="N7" s="69"/>
-      <c r="O7" s="69"/>
-      <c r="P7" s="69"/>
-      <c r="Q7" s="69"/>
-      <c r="R7" s="69"/>
-      <c r="S7" s="69"/>
-      <c r="T7" s="69"/>
-      <c r="U7" s="71"/>
+      <c r="A7" s="47"/>
+      <c r="B7" s="43"/>
+      <c r="C7" s="43"/>
+      <c r="D7" s="43"/>
+      <c r="E7" s="43"/>
+      <c r="F7" s="43"/>
+      <c r="G7" s="43"/>
+      <c r="H7" s="43"/>
+      <c r="I7" s="43"/>
+      <c r="J7" s="43"/>
+      <c r="K7" s="43"/>
+      <c r="L7" s="43"/>
+      <c r="M7" s="43"/>
+      <c r="N7" s="43"/>
+      <c r="O7" s="43"/>
+      <c r="P7" s="43"/>
+      <c r="Q7" s="43"/>
+      <c r="R7" s="43"/>
+      <c r="S7" s="43"/>
+      <c r="T7" s="43"/>
+      <c r="U7" s="48"/>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A8" s="68"/>
-      <c r="B8" s="69"/>
-      <c r="C8" s="69"/>
-      <c r="D8" s="69"/>
-      <c r="E8" s="69"/>
-      <c r="F8" s="69"/>
-      <c r="G8" s="69"/>
-      <c r="H8" s="69"/>
-      <c r="I8" s="69"/>
-      <c r="J8" s="69"/>
-      <c r="K8" s="69"/>
-      <c r="L8" s="69"/>
-      <c r="M8" s="69"/>
-      <c r="N8" s="69"/>
-      <c r="O8" s="69"/>
-      <c r="P8" s="69"/>
-      <c r="Q8" s="69"/>
-      <c r="R8" s="69"/>
-      <c r="S8" s="69"/>
-      <c r="T8" s="69"/>
-      <c r="U8" s="71"/>
+      <c r="A8" s="47"/>
+      <c r="B8" s="43"/>
+      <c r="C8" s="43"/>
+      <c r="D8" s="43"/>
+      <c r="E8" s="43"/>
+      <c r="F8" s="43"/>
+      <c r="G8" s="43"/>
+      <c r="H8" s="43"/>
+      <c r="I8" s="43"/>
+      <c r="J8" s="43"/>
+      <c r="K8" s="43"/>
+      <c r="L8" s="43"/>
+      <c r="M8" s="43"/>
+      <c r="N8" s="43"/>
+      <c r="O8" s="43"/>
+      <c r="P8" s="43"/>
+      <c r="Q8" s="43"/>
+      <c r="R8" s="43"/>
+      <c r="S8" s="43"/>
+      <c r="T8" s="43"/>
+      <c r="U8" s="48"/>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A9" s="68"/>
-      <c r="B9" s="69"/>
-      <c r="C9" s="69"/>
-      <c r="D9" s="69"/>
-      <c r="E9" s="69"/>
-      <c r="F9" s="69"/>
-      <c r="G9" s="69"/>
-      <c r="H9" s="69"/>
-      <c r="I9" s="69"/>
-      <c r="J9" s="69"/>
-      <c r="K9" s="69"/>
-      <c r="L9" s="69"/>
-      <c r="M9" s="69"/>
-      <c r="N9" s="69"/>
-      <c r="O9" s="69"/>
-      <c r="P9" s="69"/>
-      <c r="Q9" s="69"/>
-      <c r="R9" s="69"/>
-      <c r="S9" s="69"/>
-      <c r="T9" s="69"/>
-      <c r="U9" s="71"/>
+      <c r="A9" s="47"/>
+      <c r="B9" s="43"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="43"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="43"/>
+      <c r="I9" s="43"/>
+      <c r="J9" s="43"/>
+      <c r="K9" s="43"/>
+      <c r="L9" s="43"/>
+      <c r="M9" s="43"/>
+      <c r="N9" s="43"/>
+      <c r="O9" s="43"/>
+      <c r="P9" s="43"/>
+      <c r="Q9" s="43"/>
+      <c r="R9" s="43"/>
+      <c r="S9" s="43"/>
+      <c r="T9" s="43"/>
+      <c r="U9" s="48"/>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A10" s="68"/>
-      <c r="B10" s="69"/>
-      <c r="C10" s="69"/>
-      <c r="D10" s="69"/>
-      <c r="E10" s="69"/>
-      <c r="F10" s="69"/>
-      <c r="G10" s="69"/>
-      <c r="H10" s="69"/>
-      <c r="I10" s="69"/>
-      <c r="J10" s="69"/>
-      <c r="K10" s="69"/>
-      <c r="L10" s="69"/>
-      <c r="M10" s="69"/>
-      <c r="N10" s="69"/>
-      <c r="O10" s="69"/>
-      <c r="P10" s="69"/>
-      <c r="Q10" s="69"/>
-      <c r="R10" s="69"/>
-      <c r="S10" s="69"/>
-      <c r="T10" s="69"/>
-      <c r="U10" s="71"/>
+      <c r="A10" s="47"/>
+      <c r="B10" s="43"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43"/>
+      <c r="F10" s="43"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="43"/>
+      <c r="I10" s="43"/>
+      <c r="J10" s="43"/>
+      <c r="K10" s="43"/>
+      <c r="L10" s="43"/>
+      <c r="M10" s="43"/>
+      <c r="N10" s="43"/>
+      <c r="O10" s="43"/>
+      <c r="P10" s="43"/>
+      <c r="Q10" s="43"/>
+      <c r="R10" s="43"/>
+      <c r="S10" s="43"/>
+      <c r="T10" s="43"/>
+      <c r="U10" s="48"/>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A11" s="68"/>
-      <c r="B11" s="69"/>
-      <c r="C11" s="69"/>
-      <c r="D11" s="69"/>
-      <c r="E11" s="69"/>
-      <c r="F11" s="69"/>
-      <c r="G11" s="69"/>
-      <c r="H11" s="69"/>
-      <c r="I11" s="69"/>
-      <c r="J11" s="69"/>
-      <c r="K11" s="69"/>
-      <c r="L11" s="69"/>
-      <c r="M11" s="69"/>
-      <c r="N11" s="69"/>
-      <c r="O11" s="69"/>
-      <c r="P11" s="69"/>
-      <c r="Q11" s="69"/>
-      <c r="R11" s="69"/>
-      <c r="S11" s="69"/>
-      <c r="T11" s="69"/>
-      <c r="U11" s="71"/>
+      <c r="A11" s="47"/>
+      <c r="B11" s="43"/>
+      <c r="C11" s="43"/>
+      <c r="D11" s="43"/>
+      <c r="E11" s="43"/>
+      <c r="F11" s="43"/>
+      <c r="G11" s="43"/>
+      <c r="H11" s="43"/>
+      <c r="I11" s="43"/>
+      <c r="J11" s="43"/>
+      <c r="K11" s="43"/>
+      <c r="L11" s="43"/>
+      <c r="M11" s="43"/>
+      <c r="N11" s="43"/>
+      <c r="O11" s="43"/>
+      <c r="P11" s="43"/>
+      <c r="Q11" s="43"/>
+      <c r="R11" s="43"/>
+      <c r="S11" s="43"/>
+      <c r="T11" s="43"/>
+      <c r="U11" s="48"/>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A12" s="68"/>
-      <c r="B12" s="69"/>
-      <c r="C12" s="69"/>
-      <c r="D12" s="69"/>
-      <c r="E12" s="69"/>
-      <c r="F12" s="69"/>
-      <c r="G12" s="69"/>
-      <c r="H12" s="69"/>
-      <c r="I12" s="69"/>
-      <c r="J12" s="69"/>
-      <c r="K12" s="69"/>
-      <c r="L12" s="69"/>
-      <c r="M12" s="69"/>
-      <c r="N12" s="69"/>
-      <c r="O12" s="69"/>
-      <c r="P12" s="69"/>
-      <c r="Q12" s="69"/>
-      <c r="R12" s="69"/>
-      <c r="S12" s="69"/>
-      <c r="T12" s="69"/>
-      <c r="U12" s="71"/>
+      <c r="A12" s="47"/>
+      <c r="B12" s="43"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="43"/>
+      <c r="J12" s="43"/>
+      <c r="K12" s="43"/>
+      <c r="L12" s="43"/>
+      <c r="M12" s="43"/>
+      <c r="N12" s="43"/>
+      <c r="O12" s="43"/>
+      <c r="P12" s="43"/>
+      <c r="Q12" s="43"/>
+      <c r="R12" s="43"/>
+      <c r="S12" s="43"/>
+      <c r="T12" s="43"/>
+      <c r="U12" s="48"/>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A13" s="68"/>
-      <c r="B13" s="69"/>
-      <c r="C13" s="69"/>
-      <c r="D13" s="69"/>
-      <c r="E13" s="69"/>
-      <c r="F13" s="69"/>
-      <c r="G13" s="69"/>
-      <c r="H13" s="69"/>
-      <c r="I13" s="69"/>
-      <c r="J13" s="69"/>
-      <c r="K13" s="69"/>
-      <c r="L13" s="69"/>
-      <c r="M13" s="69"/>
-      <c r="N13" s="69"/>
-      <c r="O13" s="69"/>
-      <c r="P13" s="69"/>
-      <c r="Q13" s="69"/>
-      <c r="R13" s="69"/>
-      <c r="S13" s="69"/>
-      <c r="T13" s="69"/>
-      <c r="U13" s="71"/>
+      <c r="A13" s="47"/>
+      <c r="B13" s="43"/>
+      <c r="C13" s="43"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="43"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="43"/>
+      <c r="I13" s="43"/>
+      <c r="J13" s="43"/>
+      <c r="K13" s="43"/>
+      <c r="L13" s="43"/>
+      <c r="M13" s="43"/>
+      <c r="N13" s="43"/>
+      <c r="O13" s="43"/>
+      <c r="P13" s="43"/>
+      <c r="Q13" s="43"/>
+      <c r="R13" s="43"/>
+      <c r="S13" s="43"/>
+      <c r="T13" s="43"/>
+      <c r="U13" s="48"/>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A14" s="68"/>
-      <c r="B14" s="69"/>
-      <c r="C14" s="69"/>
-      <c r="D14" s="69"/>
-      <c r="E14" s="69"/>
-      <c r="F14" s="69"/>
-      <c r="G14" s="69"/>
-      <c r="H14" s="69"/>
-      <c r="I14" s="69"/>
-      <c r="J14" s="69"/>
-      <c r="K14" s="69"/>
-      <c r="L14" s="69"/>
-      <c r="M14" s="69"/>
-      <c r="N14" s="69"/>
-      <c r="O14" s="69"/>
-      <c r="P14" s="69"/>
-      <c r="Q14" s="69"/>
-      <c r="R14" s="69"/>
-      <c r="S14" s="69"/>
-      <c r="T14" s="69"/>
-      <c r="U14" s="71"/>
+      <c r="A14" s="47"/>
+      <c r="B14" s="43"/>
+      <c r="C14" s="43"/>
+      <c r="D14" s="43"/>
+      <c r="E14" s="43"/>
+      <c r="F14" s="43"/>
+      <c r="G14" s="43"/>
+      <c r="H14" s="43"/>
+      <c r="I14" s="43"/>
+      <c r="J14" s="43"/>
+      <c r="K14" s="43"/>
+      <c r="L14" s="43"/>
+      <c r="M14" s="43"/>
+      <c r="N14" s="43"/>
+      <c r="O14" s="43"/>
+      <c r="P14" s="43"/>
+      <c r="Q14" s="43"/>
+      <c r="R14" s="43"/>
+      <c r="S14" s="43"/>
+      <c r="T14" s="43"/>
+      <c r="U14" s="48"/>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A15" s="68"/>
-      <c r="B15" s="69"/>
-      <c r="C15" s="69"/>
-      <c r="D15" s="69"/>
-      <c r="E15" s="69"/>
-      <c r="F15" s="69"/>
-      <c r="G15" s="69"/>
-      <c r="H15" s="69"/>
-      <c r="I15" s="69"/>
-      <c r="J15" s="69"/>
-      <c r="K15" s="69"/>
-      <c r="L15" s="69"/>
-      <c r="M15" s="69"/>
-      <c r="N15" s="69"/>
-      <c r="O15" s="69"/>
-      <c r="P15" s="69"/>
-      <c r="Q15" s="69"/>
-      <c r="R15" s="69"/>
-      <c r="S15" s="69"/>
-      <c r="T15" s="69"/>
-      <c r="U15" s="71"/>
+      <c r="A15" s="47"/>
+      <c r="B15" s="43"/>
+      <c r="C15" s="43"/>
+      <c r="D15" s="43"/>
+      <c r="E15" s="43"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="43"/>
+      <c r="H15" s="43"/>
+      <c r="I15" s="43"/>
+      <c r="J15" s="43"/>
+      <c r="K15" s="43"/>
+      <c r="L15" s="43"/>
+      <c r="M15" s="43"/>
+      <c r="N15" s="43"/>
+      <c r="O15" s="43"/>
+      <c r="P15" s="43"/>
+      <c r="Q15" s="43"/>
+      <c r="R15" s="43"/>
+      <c r="S15" s="43"/>
+      <c r="T15" s="43"/>
+      <c r="U15" s="48"/>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A16" s="68"/>
-      <c r="B16" s="69"/>
-      <c r="C16" s="69"/>
-      <c r="D16" s="69"/>
-      <c r="E16" s="69"/>
-      <c r="F16" s="69"/>
-      <c r="G16" s="69"/>
-      <c r="H16" s="69"/>
-      <c r="I16" s="69"/>
-      <c r="J16" s="69"/>
-      <c r="K16" s="69"/>
-      <c r="L16" s="69"/>
-      <c r="M16" s="69"/>
-      <c r="N16" s="69"/>
-      <c r="O16" s="69"/>
-      <c r="P16" s="69"/>
-      <c r="Q16" s="69"/>
-      <c r="R16" s="69"/>
-      <c r="S16" s="69"/>
-      <c r="T16" s="69"/>
-      <c r="U16" s="71"/>
+      <c r="A16" s="47"/>
+      <c r="B16" s="43"/>
+      <c r="C16" s="43"/>
+      <c r="D16" s="43"/>
+      <c r="E16" s="43"/>
+      <c r="F16" s="43"/>
+      <c r="G16" s="43"/>
+      <c r="H16" s="43"/>
+      <c r="I16" s="43"/>
+      <c r="J16" s="43"/>
+      <c r="K16" s="43"/>
+      <c r="L16" s="43"/>
+      <c r="M16" s="43"/>
+      <c r="N16" s="43"/>
+      <c r="O16" s="43"/>
+      <c r="P16" s="43"/>
+      <c r="Q16" s="43"/>
+      <c r="R16" s="43"/>
+      <c r="S16" s="43"/>
+      <c r="T16" s="43"/>
+      <c r="U16" s="48"/>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A17" s="68"/>
-      <c r="B17" s="69"/>
-      <c r="C17" s="69"/>
-      <c r="D17" s="69"/>
-      <c r="E17" s="69"/>
-      <c r="F17" s="69"/>
-      <c r="G17" s="69"/>
-      <c r="H17" s="69"/>
-      <c r="I17" s="69"/>
-      <c r="J17" s="69"/>
-      <c r="K17" s="69"/>
-      <c r="L17" s="69"/>
-      <c r="M17" s="69"/>
-      <c r="N17" s="69"/>
-      <c r="O17" s="69"/>
-      <c r="P17" s="69"/>
-      <c r="Q17" s="69"/>
-      <c r="R17" s="69"/>
-      <c r="S17" s="69"/>
-      <c r="T17" s="69"/>
-      <c r="U17" s="71"/>
+      <c r="A17" s="47"/>
+      <c r="B17" s="43"/>
+      <c r="C17" s="43"/>
+      <c r="D17" s="43"/>
+      <c r="E17" s="43"/>
+      <c r="F17" s="43"/>
+      <c r="G17" s="43"/>
+      <c r="H17" s="43"/>
+      <c r="I17" s="43"/>
+      <c r="J17" s="43"/>
+      <c r="K17" s="43"/>
+      <c r="L17" s="43"/>
+      <c r="M17" s="43"/>
+      <c r="N17" s="43"/>
+      <c r="O17" s="43"/>
+      <c r="P17" s="43"/>
+      <c r="Q17" s="43"/>
+      <c r="R17" s="43"/>
+      <c r="S17" s="43"/>
+      <c r="T17" s="43"/>
+      <c r="U17" s="48"/>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A18" s="68"/>
-      <c r="B18" s="69"/>
-      <c r="C18" s="69"/>
-      <c r="D18" s="69"/>
-      <c r="E18" s="69"/>
-      <c r="F18" s="69"/>
-      <c r="G18" s="69"/>
-      <c r="H18" s="69"/>
-      <c r="I18" s="69"/>
-      <c r="J18" s="69"/>
-      <c r="K18" s="69"/>
-      <c r="L18" s="69"/>
-      <c r="M18" s="69"/>
-      <c r="N18" s="69"/>
-      <c r="O18" s="69"/>
-      <c r="P18" s="69"/>
-      <c r="Q18" s="69"/>
-      <c r="R18" s="69"/>
-      <c r="S18" s="69"/>
-      <c r="T18" s="69"/>
-      <c r="U18" s="71"/>
+      <c r="A18" s="47"/>
+      <c r="B18" s="43"/>
+      <c r="C18" s="43"/>
+      <c r="D18" s="43"/>
+      <c r="E18" s="43"/>
+      <c r="F18" s="43"/>
+      <c r="G18" s="43"/>
+      <c r="H18" s="43"/>
+      <c r="I18" s="43"/>
+      <c r="J18" s="43"/>
+      <c r="K18" s="43"/>
+      <c r="L18" s="43"/>
+      <c r="M18" s="43"/>
+      <c r="N18" s="43"/>
+      <c r="O18" s="43"/>
+      <c r="P18" s="43"/>
+      <c r="Q18" s="43"/>
+      <c r="R18" s="43"/>
+      <c r="S18" s="43"/>
+      <c r="T18" s="43"/>
+      <c r="U18" s="48"/>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A19" s="68"/>
-      <c r="B19" s="69"/>
-      <c r="C19" s="69"/>
-      <c r="D19" s="69"/>
-      <c r="E19" s="69"/>
-      <c r="F19" s="69"/>
-      <c r="G19" s="69"/>
-      <c r="H19" s="69"/>
-      <c r="I19" s="69"/>
-      <c r="J19" s="69"/>
-      <c r="K19" s="69"/>
-      <c r="L19" s="69"/>
-      <c r="M19" s="69"/>
-      <c r="N19" s="69"/>
-      <c r="O19" s="69"/>
-      <c r="P19" s="69"/>
-      <c r="Q19" s="69"/>
-      <c r="R19" s="69"/>
-      <c r="S19" s="69"/>
-      <c r="T19" s="69"/>
-      <c r="U19" s="71"/>
+      <c r="A19" s="47"/>
+      <c r="B19" s="43"/>
+      <c r="C19" s="43"/>
+      <c r="D19" s="43"/>
+      <c r="E19" s="43"/>
+      <c r="F19" s="43"/>
+      <c r="G19" s="43"/>
+      <c r="H19" s="43"/>
+      <c r="I19" s="43"/>
+      <c r="J19" s="43"/>
+      <c r="K19" s="43"/>
+      <c r="L19" s="43"/>
+      <c r="M19" s="43"/>
+      <c r="N19" s="43"/>
+      <c r="O19" s="43"/>
+      <c r="P19" s="43"/>
+      <c r="Q19" s="43"/>
+      <c r="R19" s="43"/>
+      <c r="S19" s="43"/>
+      <c r="T19" s="43"/>
+      <c r="U19" s="48"/>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A20" s="68"/>
-      <c r="B20" s="69"/>
-      <c r="C20" s="69"/>
-      <c r="D20" s="69"/>
-      <c r="E20" s="69"/>
-      <c r="F20" s="69"/>
-      <c r="G20" s="69"/>
-      <c r="H20" s="69"/>
-      <c r="I20" s="69"/>
-      <c r="J20" s="69"/>
-      <c r="K20" s="69"/>
-      <c r="L20" s="69"/>
-      <c r="M20" s="69"/>
-      <c r="N20" s="69"/>
-      <c r="O20" s="69"/>
-      <c r="P20" s="69"/>
-      <c r="Q20" s="69"/>
-      <c r="R20" s="69"/>
-      <c r="S20" s="69"/>
-      <c r="T20" s="69"/>
-      <c r="U20" s="71"/>
+      <c r="A20" s="47"/>
+      <c r="B20" s="43"/>
+      <c r="C20" s="43"/>
+      <c r="D20" s="43"/>
+      <c r="E20" s="43"/>
+      <c r="F20" s="43"/>
+      <c r="G20" s="43"/>
+      <c r="H20" s="43"/>
+      <c r="I20" s="43"/>
+      <c r="J20" s="43"/>
+      <c r="K20" s="43"/>
+      <c r="L20" s="43"/>
+      <c r="M20" s="43"/>
+      <c r="N20" s="43"/>
+      <c r="O20" s="43"/>
+      <c r="P20" s="43"/>
+      <c r="Q20" s="43"/>
+      <c r="R20" s="43"/>
+      <c r="S20" s="43"/>
+      <c r="T20" s="43"/>
+      <c r="U20" s="48"/>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A21" s="68"/>
-      <c r="B21" s="69"/>
-      <c r="C21" s="69"/>
-      <c r="D21" s="69"/>
-      <c r="E21" s="69"/>
-      <c r="F21" s="69"/>
-      <c r="G21" s="69"/>
-      <c r="H21" s="69"/>
-      <c r="I21" s="69"/>
-      <c r="J21" s="69"/>
-      <c r="K21" s="69"/>
-      <c r="L21" s="69"/>
-      <c r="M21" s="69"/>
-      <c r="N21" s="69"/>
-      <c r="O21" s="69"/>
-      <c r="P21" s="69"/>
-      <c r="Q21" s="69"/>
-      <c r="R21" s="69"/>
-      <c r="S21" s="69"/>
-      <c r="T21" s="69"/>
-      <c r="U21" s="71"/>
+      <c r="A21" s="47"/>
+      <c r="B21" s="43"/>
+      <c r="C21" s="43"/>
+      <c r="D21" s="43"/>
+      <c r="E21" s="43"/>
+      <c r="F21" s="43"/>
+      <c r="G21" s="43"/>
+      <c r="H21" s="43"/>
+      <c r="I21" s="43"/>
+      <c r="J21" s="43"/>
+      <c r="K21" s="43"/>
+      <c r="L21" s="43"/>
+      <c r="M21" s="43"/>
+      <c r="N21" s="43"/>
+      <c r="O21" s="43"/>
+      <c r="P21" s="43"/>
+      <c r="Q21" s="43"/>
+      <c r="R21" s="43"/>
+      <c r="S21" s="43"/>
+      <c r="T21" s="43"/>
+      <c r="U21" s="48"/>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A22" s="68"/>
-      <c r="B22" s="69"/>
-      <c r="C22" s="69"/>
-      <c r="D22" s="69"/>
-      <c r="E22" s="69"/>
-      <c r="F22" s="69"/>
-      <c r="G22" s="69"/>
-      <c r="H22" s="69"/>
-      <c r="I22" s="69"/>
-      <c r="J22" s="69"/>
-      <c r="K22" s="69"/>
-      <c r="L22" s="69"/>
-      <c r="M22" s="69"/>
-      <c r="N22" s="69"/>
-      <c r="O22" s="69"/>
-      <c r="P22" s="69"/>
-      <c r="Q22" s="69"/>
-      <c r="R22" s="69"/>
-      <c r="S22" s="69"/>
-      <c r="T22" s="69"/>
-      <c r="U22" s="71"/>
+      <c r="A22" s="47"/>
+      <c r="B22" s="43"/>
+      <c r="C22" s="43"/>
+      <c r="D22" s="43"/>
+      <c r="E22" s="43"/>
+      <c r="F22" s="43"/>
+      <c r="G22" s="43"/>
+      <c r="H22" s="43"/>
+      <c r="I22" s="43"/>
+      <c r="J22" s="43"/>
+      <c r="K22" s="43"/>
+      <c r="L22" s="43"/>
+      <c r="M22" s="43"/>
+      <c r="N22" s="43"/>
+      <c r="O22" s="43"/>
+      <c r="P22" s="43"/>
+      <c r="Q22" s="43"/>
+      <c r="R22" s="43"/>
+      <c r="S22" s="43"/>
+      <c r="T22" s="43"/>
+      <c r="U22" s="48"/>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A23" s="68"/>
-      <c r="B23" s="69"/>
-      <c r="C23" s="69"/>
-      <c r="D23" s="69"/>
-      <c r="E23" s="69"/>
-      <c r="F23" s="69"/>
-      <c r="G23" s="69"/>
-      <c r="H23" s="69"/>
-      <c r="I23" s="69"/>
-      <c r="J23" s="69"/>
-      <c r="K23" s="69"/>
-      <c r="L23" s="69"/>
-      <c r="M23" s="69"/>
-      <c r="N23" s="69"/>
-      <c r="O23" s="69"/>
-      <c r="P23" s="69"/>
-      <c r="Q23" s="69"/>
-      <c r="R23" s="69"/>
-      <c r="S23" s="69"/>
-      <c r="T23" s="69"/>
-      <c r="U23" s="71"/>
+      <c r="A23" s="47"/>
+      <c r="B23" s="43"/>
+      <c r="C23" s="43"/>
+      <c r="D23" s="43"/>
+      <c r="E23" s="43"/>
+      <c r="F23" s="43"/>
+      <c r="G23" s="43"/>
+      <c r="H23" s="43"/>
+      <c r="I23" s="43"/>
+      <c r="J23" s="43"/>
+      <c r="K23" s="43"/>
+      <c r="L23" s="43"/>
+      <c r="M23" s="43"/>
+      <c r="N23" s="43"/>
+      <c r="O23" s="43"/>
+      <c r="P23" s="43"/>
+      <c r="Q23" s="43"/>
+      <c r="R23" s="43"/>
+      <c r="S23" s="43"/>
+      <c r="T23" s="43"/>
+      <c r="U23" s="48"/>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A24" s="68"/>
-      <c r="B24" s="69"/>
-      <c r="C24" s="69"/>
-      <c r="D24" s="69"/>
-      <c r="E24" s="69"/>
-      <c r="F24" s="69"/>
-      <c r="G24" s="69"/>
-      <c r="H24" s="69"/>
-      <c r="I24" s="69"/>
-      <c r="J24" s="69"/>
-      <c r="K24" s="69"/>
-      <c r="L24" s="69"/>
-      <c r="M24" s="69"/>
-      <c r="N24" s="69"/>
-      <c r="O24" s="69"/>
-      <c r="P24" s="69"/>
-      <c r="Q24" s="69"/>
-      <c r="R24" s="69"/>
-      <c r="S24" s="69"/>
-      <c r="T24" s="69"/>
-      <c r="U24" s="71"/>
+      <c r="A24" s="47"/>
+      <c r="B24" s="43"/>
+      <c r="C24" s="43"/>
+      <c r="D24" s="43"/>
+      <c r="E24" s="43"/>
+      <c r="F24" s="43"/>
+      <c r="G24" s="43"/>
+      <c r="H24" s="43"/>
+      <c r="I24" s="43"/>
+      <c r="J24" s="43"/>
+      <c r="K24" s="43"/>
+      <c r="L24" s="43"/>
+      <c r="M24" s="43"/>
+      <c r="N24" s="43"/>
+      <c r="O24" s="43"/>
+      <c r="P24" s="43"/>
+      <c r="Q24" s="43"/>
+      <c r="R24" s="43"/>
+      <c r="S24" s="43"/>
+      <c r="T24" s="43"/>
+      <c r="U24" s="48"/>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A25" s="68"/>
-      <c r="B25" s="69"/>
-      <c r="C25" s="69"/>
-      <c r="D25" s="69"/>
-      <c r="E25" s="69"/>
-      <c r="F25" s="69"/>
-      <c r="G25" s="69"/>
-      <c r="H25" s="69"/>
-      <c r="I25" s="69"/>
-      <c r="J25" s="69"/>
-      <c r="K25" s="69"/>
-      <c r="L25" s="69"/>
-      <c r="M25" s="69"/>
-      <c r="N25" s="69"/>
-      <c r="O25" s="69"/>
-      <c r="P25" s="69"/>
-      <c r="Q25" s="69"/>
-      <c r="R25" s="69"/>
-      <c r="S25" s="69"/>
-      <c r="T25" s="69"/>
-      <c r="U25" s="71"/>
+      <c r="A25" s="47"/>
+      <c r="B25" s="43"/>
+      <c r="C25" s="43"/>
+      <c r="D25" s="43"/>
+      <c r="E25" s="43"/>
+      <c r="F25" s="43"/>
+      <c r="G25" s="43"/>
+      <c r="H25" s="43"/>
+      <c r="I25" s="43"/>
+      <c r="J25" s="43"/>
+      <c r="K25" s="43"/>
+      <c r="L25" s="43"/>
+      <c r="M25" s="43"/>
+      <c r="N25" s="43"/>
+      <c r="O25" s="43"/>
+      <c r="P25" s="43"/>
+      <c r="Q25" s="43"/>
+      <c r="R25" s="43"/>
+      <c r="S25" s="43"/>
+      <c r="T25" s="43"/>
+      <c r="U25" s="48"/>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A26" s="68"/>
-      <c r="B26" s="69"/>
-      <c r="C26" s="69"/>
-      <c r="D26" s="69"/>
-      <c r="E26" s="69"/>
-      <c r="F26" s="69"/>
-      <c r="G26" s="69"/>
-      <c r="H26" s="69"/>
-      <c r="I26" s="69"/>
-      <c r="J26" s="69"/>
-      <c r="K26" s="69"/>
-      <c r="L26" s="69"/>
-      <c r="M26" s="69"/>
-      <c r="N26" s="69"/>
-      <c r="O26" s="69"/>
-      <c r="P26" s="69"/>
-      <c r="Q26" s="69"/>
-      <c r="R26" s="69"/>
-      <c r="S26" s="69"/>
-      <c r="T26" s="69"/>
-      <c r="U26" s="71"/>
+      <c r="A26" s="47"/>
+      <c r="B26" s="43"/>
+      <c r="C26" s="43"/>
+      <c r="D26" s="43"/>
+      <c r="E26" s="43"/>
+      <c r="F26" s="43"/>
+      <c r="G26" s="43"/>
+      <c r="H26" s="43"/>
+      <c r="I26" s="43"/>
+      <c r="J26" s="43"/>
+      <c r="K26" s="43"/>
+      <c r="L26" s="43"/>
+      <c r="M26" s="43"/>
+      <c r="N26" s="43"/>
+      <c r="O26" s="43"/>
+      <c r="P26" s="43"/>
+      <c r="Q26" s="43"/>
+      <c r="R26" s="43"/>
+      <c r="S26" s="43"/>
+      <c r="T26" s="43"/>
+      <c r="U26" s="48"/>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A27" s="68"/>
-      <c r="B27" s="69"/>
-      <c r="C27" s="69"/>
-      <c r="D27" s="69"/>
-      <c r="E27" s="69"/>
-      <c r="F27" s="69"/>
-      <c r="G27" s="69"/>
-      <c r="H27" s="69"/>
-      <c r="I27" s="69"/>
-      <c r="J27" s="69"/>
-      <c r="K27" s="69"/>
-      <c r="L27" s="69"/>
-      <c r="M27" s="69"/>
-      <c r="N27" s="69"/>
-      <c r="O27" s="69"/>
-      <c r="P27" s="69"/>
-      <c r="Q27" s="69"/>
-      <c r="R27" s="69"/>
-      <c r="S27" s="69"/>
-      <c r="T27" s="69"/>
-      <c r="U27" s="71"/>
+      <c r="A27" s="47"/>
+      <c r="B27" s="43"/>
+      <c r="C27" s="43"/>
+      <c r="D27" s="43"/>
+      <c r="E27" s="43"/>
+      <c r="F27" s="43"/>
+      <c r="G27" s="43"/>
+      <c r="H27" s="43"/>
+      <c r="I27" s="43"/>
+      <c r="J27" s="43"/>
+      <c r="K27" s="43"/>
+      <c r="L27" s="43"/>
+      <c r="M27" s="43"/>
+      <c r="N27" s="43"/>
+      <c r="O27" s="43"/>
+      <c r="P27" s="43"/>
+      <c r="Q27" s="43"/>
+      <c r="R27" s="43"/>
+      <c r="S27" s="43"/>
+      <c r="T27" s="43"/>
+      <c r="U27" s="48"/>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A28" s="68"/>
-      <c r="B28" s="69"/>
-      <c r="C28" s="69"/>
-      <c r="D28" s="69"/>
-      <c r="E28" s="69"/>
-      <c r="F28" s="69"/>
-      <c r="G28" s="69"/>
-      <c r="H28" s="69"/>
-      <c r="I28" s="69"/>
-      <c r="J28" s="69"/>
-      <c r="K28" s="69"/>
-      <c r="L28" s="69"/>
-      <c r="M28" s="69"/>
-      <c r="N28" s="69"/>
-      <c r="O28" s="69"/>
-      <c r="P28" s="69"/>
-      <c r="Q28" s="69"/>
-      <c r="R28" s="69"/>
-      <c r="S28" s="69"/>
-      <c r="T28" s="69"/>
-      <c r="U28" s="71"/>
+      <c r="A28" s="47"/>
+      <c r="B28" s="43"/>
+      <c r="C28" s="43"/>
+      <c r="D28" s="43"/>
+      <c r="E28" s="43"/>
+      <c r="F28" s="43"/>
+      <c r="G28" s="43"/>
+      <c r="H28" s="43"/>
+      <c r="I28" s="43"/>
+      <c r="J28" s="43"/>
+      <c r="K28" s="43"/>
+      <c r="L28" s="43"/>
+      <c r="M28" s="43"/>
+      <c r="N28" s="43"/>
+      <c r="O28" s="43"/>
+      <c r="P28" s="43"/>
+      <c r="Q28" s="43"/>
+      <c r="R28" s="43"/>
+      <c r="S28" s="43"/>
+      <c r="T28" s="43"/>
+      <c r="U28" s="48"/>
     </row>
     <row r="29" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="76"/>
-      <c r="B29" s="73"/>
-      <c r="C29" s="73"/>
-      <c r="D29" s="73"/>
-      <c r="E29" s="73"/>
-      <c r="F29" s="73"/>
-      <c r="G29" s="73"/>
-      <c r="H29" s="73"/>
-      <c r="I29" s="73"/>
-      <c r="J29" s="73"/>
-      <c r="K29" s="73"/>
-      <c r="L29" s="73"/>
-      <c r="M29" s="73"/>
-      <c r="N29" s="73"/>
-      <c r="O29" s="73"/>
-      <c r="P29" s="73"/>
-      <c r="Q29" s="73"/>
-      <c r="R29" s="73"/>
-      <c r="S29" s="73"/>
-      <c r="T29" s="73"/>
-      <c r="U29" s="74"/>
+      <c r="A29" s="52"/>
+      <c r="B29" s="50"/>
+      <c r="C29" s="50"/>
+      <c r="D29" s="50"/>
+      <c r="E29" s="50"/>
+      <c r="F29" s="50"/>
+      <c r="G29" s="50"/>
+      <c r="H29" s="50"/>
+      <c r="I29" s="50"/>
+      <c r="J29" s="50"/>
+      <c r="K29" s="50"/>
+      <c r="L29" s="50"/>
+      <c r="M29" s="50"/>
+      <c r="N29" s="50"/>
+      <c r="O29" s="50"/>
+      <c r="P29" s="50"/>
+      <c r="Q29" s="50"/>
+      <c r="R29" s="50"/>
+      <c r="S29" s="50"/>
+      <c r="T29" s="50"/>
+      <c r="U29" s="51"/>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A30" s="64"/>
-      <c r="B30" s="64"/>
-      <c r="C30" s="64"/>
-      <c r="D30" s="64"/>
-      <c r="E30" s="64"/>
-      <c r="F30" s="64"/>
-      <c r="G30" s="64"/>
-      <c r="H30" s="64"/>
-      <c r="I30" s="64"/>
-      <c r="J30" s="64"/>
-      <c r="K30" s="64"/>
-      <c r="L30" s="64"/>
-      <c r="M30" s="64"/>
-      <c r="N30" s="64"/>
-      <c r="O30" s="64"/>
-      <c r="P30" s="64"/>
-      <c r="Q30" s="64"/>
-      <c r="R30" s="64"/>
-      <c r="S30" s="64"/>
-      <c r="T30" s="64"/>
-      <c r="U30" s="64"/>
-    </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A31" s="75"/>
-      <c r="B31" s="75"/>
-      <c r="C31" s="75"/>
-      <c r="D31" s="75"/>
-      <c r="E31" s="75"/>
-      <c r="F31" s="75"/>
-      <c r="G31" s="75"/>
-      <c r="H31" s="75"/>
-      <c r="I31" s="75"/>
-      <c r="J31" s="75"/>
-      <c r="K31" s="75"/>
-      <c r="L31" s="75"/>
-      <c r="M31" s="75"/>
-      <c r="N31" s="75"/>
-      <c r="O31" s="75"/>
-      <c r="P31" s="75"/>
-      <c r="Q31" s="75"/>
-      <c r="R31" s="75"/>
-      <c r="S31" s="75"/>
-      <c r="T31" s="75"/>
-      <c r="U31" s="75"/>
-    </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A32" s="75"/>
-      <c r="B32" s="75"/>
-      <c r="C32" s="75"/>
-      <c r="D32" s="75"/>
-      <c r="E32" s="75"/>
-      <c r="F32" s="75"/>
-      <c r="G32" s="75"/>
-      <c r="H32" s="75"/>
-      <c r="I32" s="75"/>
-      <c r="J32" s="75"/>
-      <c r="K32" s="75"/>
-      <c r="L32" s="75"/>
-      <c r="M32" s="75"/>
-      <c r="N32" s="75"/>
-      <c r="O32" s="75"/>
-      <c r="P32" s="75"/>
-      <c r="Q32" s="75"/>
-      <c r="R32" s="75"/>
-      <c r="S32" s="75"/>
-      <c r="T32" s="75"/>
-      <c r="U32" s="75"/>
-    </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A33" s="75"/>
-      <c r="B33" s="75"/>
-      <c r="C33" s="75"/>
-      <c r="D33" s="75"/>
-      <c r="E33" s="75"/>
-      <c r="F33" s="75"/>
-      <c r="G33" s="75"/>
-      <c r="H33" s="75"/>
-      <c r="I33" s="75"/>
-      <c r="J33" s="75"/>
-      <c r="K33" s="75"/>
-      <c r="L33" s="75"/>
-      <c r="M33" s="75"/>
-      <c r="N33" s="75"/>
-      <c r="O33" s="75"/>
-      <c r="P33" s="75"/>
-      <c r="Q33" s="75"/>
-      <c r="R33" s="75"/>
-      <c r="S33" s="75"/>
-      <c r="T33" s="75"/>
-      <c r="U33" s="75"/>
-    </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A34" s="75"/>
-      <c r="B34" s="75"/>
-      <c r="C34" s="75"/>
-      <c r="D34" s="75"/>
-      <c r="E34" s="75"/>
-      <c r="F34" s="75"/>
-      <c r="G34" s="75"/>
-      <c r="H34" s="75"/>
-      <c r="I34" s="75"/>
-      <c r="J34" s="75"/>
-      <c r="K34" s="75"/>
-      <c r="L34" s="75"/>
-      <c r="M34" s="75"/>
-      <c r="N34" s="75"/>
-      <c r="O34" s="75"/>
-      <c r="P34" s="75"/>
-      <c r="Q34" s="75"/>
-      <c r="R34" s="75"/>
-      <c r="S34" s="75"/>
-      <c r="T34" s="75"/>
-      <c r="U34" s="75"/>
-    </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A35" s="75"/>
-      <c r="B35" s="75"/>
-      <c r="C35" s="75"/>
-      <c r="D35" s="75"/>
-      <c r="E35" s="75"/>
-      <c r="F35" s="75"/>
-      <c r="G35" s="75"/>
-      <c r="H35" s="75"/>
-      <c r="I35" s="75"/>
-      <c r="J35" s="75"/>
-      <c r="K35" s="75"/>
-      <c r="L35" s="75"/>
-      <c r="M35" s="75"/>
-      <c r="N35" s="75"/>
-      <c r="O35" s="75"/>
-      <c r="P35" s="75"/>
-      <c r="Q35" s="75"/>
-      <c r="R35" s="75"/>
-      <c r="S35" s="75"/>
-      <c r="T35" s="75"/>
-      <c r="U35" s="75"/>
-    </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A36" s="75"/>
-      <c r="B36" s="75"/>
-      <c r="C36" s="75"/>
-      <c r="D36" s="75"/>
-      <c r="E36" s="75"/>
-      <c r="F36" s="75"/>
-      <c r="G36" s="75"/>
-      <c r="H36" s="75"/>
-      <c r="I36" s="75"/>
-      <c r="J36" s="75"/>
-      <c r="K36" s="75"/>
-      <c r="L36" s="75"/>
-      <c r="M36" s="75"/>
-      <c r="N36" s="75"/>
-      <c r="O36" s="75"/>
-      <c r="P36" s="75"/>
-      <c r="Q36" s="75"/>
-      <c r="R36" s="75"/>
-      <c r="S36" s="75"/>
-      <c r="T36" s="75"/>
-      <c r="U36" s="75"/>
-    </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A37" s="75"/>
-      <c r="B37" s="75"/>
-      <c r="C37" s="75"/>
-      <c r="D37" s="75"/>
-      <c r="E37" s="75"/>
-      <c r="F37" s="75"/>
-      <c r="G37" s="75"/>
-      <c r="H37" s="75"/>
-      <c r="I37" s="75"/>
-      <c r="J37" s="75"/>
-      <c r="K37" s="75"/>
-      <c r="L37" s="75"/>
-      <c r="M37" s="75"/>
-      <c r="N37" s="75"/>
-      <c r="O37" s="75"/>
-      <c r="P37" s="75"/>
-      <c r="Q37" s="75"/>
-      <c r="R37" s="75"/>
-      <c r="S37" s="75"/>
-      <c r="T37" s="75"/>
-      <c r="U37" s="75"/>
-    </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A38" s="75"/>
-      <c r="B38" s="75"/>
-      <c r="C38" s="75"/>
-      <c r="D38" s="75"/>
-      <c r="E38" s="75"/>
-      <c r="F38" s="75"/>
-      <c r="G38" s="75"/>
-      <c r="H38" s="75"/>
-      <c r="I38" s="75"/>
-      <c r="J38" s="75"/>
-      <c r="K38" s="75"/>
-      <c r="L38" s="75"/>
-      <c r="M38" s="75"/>
-      <c r="N38" s="75"/>
-      <c r="O38" s="75"/>
-      <c r="P38" s="75"/>
-      <c r="Q38" s="75"/>
-      <c r="R38" s="75"/>
-      <c r="S38" s="75"/>
-      <c r="T38" s="75"/>
-      <c r="U38" s="75"/>
-    </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A39" s="75"/>
-      <c r="B39" s="75"/>
-      <c r="C39" s="75"/>
-      <c r="D39" s="75"/>
-      <c r="E39" s="75"/>
-      <c r="F39" s="75"/>
-      <c r="G39" s="75"/>
-      <c r="H39" s="75"/>
-      <c r="I39" s="75"/>
-      <c r="J39" s="75"/>
-      <c r="K39" s="75"/>
-      <c r="L39" s="75"/>
-      <c r="M39" s="75"/>
-      <c r="N39" s="75"/>
-      <c r="O39" s="75"/>
-      <c r="P39" s="75"/>
-      <c r="Q39" s="75"/>
-      <c r="R39" s="75"/>
-      <c r="S39" s="75"/>
-      <c r="T39" s="75"/>
-      <c r="U39" s="75"/>
-    </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A40" s="75"/>
-      <c r="B40" s="75"/>
-      <c r="C40" s="75"/>
-      <c r="D40" s="75"/>
-      <c r="E40" s="75"/>
-      <c r="F40" s="75"/>
-      <c r="G40" s="75"/>
-      <c r="H40" s="75"/>
-      <c r="I40" s="75"/>
-      <c r="J40" s="75"/>
-      <c r="K40" s="75"/>
-      <c r="L40" s="75"/>
-      <c r="M40" s="75"/>
-      <c r="N40" s="75"/>
-      <c r="O40" s="75"/>
-      <c r="P40" s="75"/>
-      <c r="Q40" s="75"/>
-      <c r="R40" s="75"/>
-      <c r="S40" s="75"/>
-      <c r="T40" s="75"/>
-      <c r="U40" s="75"/>
-    </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A41" s="75"/>
-      <c r="B41" s="75"/>
-      <c r="C41" s="75"/>
-      <c r="D41" s="75"/>
-      <c r="E41" s="75"/>
-      <c r="F41" s="75"/>
-      <c r="G41" s="75"/>
-      <c r="H41" s="75"/>
-      <c r="I41" s="75"/>
-      <c r="J41" s="75"/>
-      <c r="K41" s="75"/>
-      <c r="L41" s="75"/>
-      <c r="M41" s="75"/>
-      <c r="N41" s="75"/>
-      <c r="O41" s="75"/>
-      <c r="P41" s="75"/>
-      <c r="Q41" s="75"/>
-      <c r="R41" s="75"/>
-      <c r="S41" s="75"/>
-      <c r="T41" s="75"/>
-      <c r="U41" s="75"/>
+      <c r="A30" s="43"/>
+      <c r="B30" s="43"/>
+      <c r="C30" s="43"/>
+      <c r="D30" s="43"/>
+      <c r="E30" s="43"/>
+      <c r="F30" s="43"/>
+      <c r="G30" s="43"/>
+      <c r="H30" s="43"/>
+      <c r="I30" s="43"/>
+      <c r="J30" s="43"/>
+      <c r="K30" s="43"/>
+      <c r="L30" s="43"/>
+      <c r="M30" s="43"/>
+      <c r="N30" s="43"/>
+      <c r="O30" s="43"/>
+      <c r="P30" s="43"/>
+      <c r="Q30" s="43"/>
+      <c r="R30" s="43"/>
+      <c r="S30" s="43"/>
+      <c r="T30" s="43"/>
+      <c r="U30" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3373,6 +3742,660 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCB4D1DF-FD9A-427C-B043-7ED5583A7DE4}">
+  <dimension ref="A1:N21"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="11" max="11" width="15.453125" customWidth="1"/>
+    <col min="12" max="12" width="19.1796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A1" s="15"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+    </row>
+    <row r="2" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="15"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="15"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A3" s="15"/>
+      <c r="B3" s="80" t="s">
+        <v>183</v>
+      </c>
+      <c r="C3" s="81"/>
+      <c r="D3" s="81"/>
+      <c r="E3" s="81"/>
+      <c r="F3" s="81"/>
+      <c r="G3" s="81"/>
+      <c r="H3" s="82"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="15"/>
+      <c r="K3" s="15"/>
+      <c r="L3" s="15"/>
+      <c r="M3" s="15"/>
+      <c r="N3" s="15"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A4" s="15"/>
+      <c r="B4" s="83"/>
+      <c r="C4" s="84"/>
+      <c r="D4" s="84"/>
+      <c r="E4" s="84"/>
+      <c r="F4" s="84"/>
+      <c r="G4" s="84"/>
+      <c r="H4" s="85"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="15"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="15"/>
+    </row>
+    <row r="5" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="15"/>
+      <c r="B5" s="86"/>
+      <c r="C5" s="87"/>
+      <c r="D5" s="87"/>
+      <c r="E5" s="87"/>
+      <c r="F5" s="87"/>
+      <c r="G5" s="87"/>
+      <c r="H5" s="88"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="15"/>
+      <c r="K5" s="15"/>
+      <c r="L5" s="15"/>
+      <c r="M5" s="15"/>
+      <c r="N5" s="15"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A6" s="15"/>
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="15"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A7" s="15"/>
+      <c r="B7" s="68" t="s">
+        <v>155</v>
+      </c>
+      <c r="C7" s="69">
+        <v>2026</v>
+      </c>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="15"/>
+      <c r="G7" s="15"/>
+      <c r="H7" s="15"/>
+      <c r="I7" s="15"/>
+      <c r="J7" s="15"/>
+      <c r="K7" s="115"/>
+      <c r="L7" s="15"/>
+      <c r="M7" s="15"/>
+      <c r="N7" s="15"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A8" s="15"/>
+      <c r="B8" s="68" t="s">
+        <v>156</v>
+      </c>
+      <c r="C8" s="69" t="s">
+        <v>157</v>
+      </c>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="15"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="15"/>
+      <c r="M8" s="15"/>
+      <c r="N8" s="15"/>
+    </row>
+    <row r="9" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="15"/>
+      <c r="B9" s="15"/>
+      <c r="C9" s="15"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="15"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="15"/>
+      <c r="J9" s="15"/>
+      <c r="K9" s="15"/>
+      <c r="L9" s="15"/>
+      <c r="M9" s="15"/>
+      <c r="N9" s="15"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A10" s="15"/>
+      <c r="B10" t="s">
+        <v>158</v>
+      </c>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="70" t="s">
+        <v>159</v>
+      </c>
+      <c r="K10" s="71" t="s">
+        <v>160</v>
+      </c>
+      <c r="L10" s="71" t="s">
+        <v>171</v>
+      </c>
+      <c r="M10" s="72" t="s">
+        <v>178</v>
+      </c>
+      <c r="N10" s="15"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A11" s="15"/>
+      <c r="B11" s="68" t="s">
+        <v>161</v>
+      </c>
+      <c r="C11" s="68" t="s">
+        <v>162</v>
+      </c>
+      <c r="D11" s="68" t="s">
+        <v>163</v>
+      </c>
+      <c r="E11" s="68" t="s">
+        <v>164</v>
+      </c>
+      <c r="F11" s="68" t="s">
+        <v>165</v>
+      </c>
+      <c r="G11" s="68" t="s">
+        <v>166</v>
+      </c>
+      <c r="H11" s="68" t="s">
+        <v>167</v>
+      </c>
+      <c r="I11" s="15"/>
+      <c r="J11" s="73">
+        <v>0.625</v>
+      </c>
+      <c r="K11" s="69" t="s">
+        <v>168</v>
+      </c>
+      <c r="L11" s="69"/>
+      <c r="M11" s="74"/>
+      <c r="N11" s="15"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A12" s="15"/>
+      <c r="B12" s="69">
+        <v>29</v>
+      </c>
+      <c r="C12" s="69">
+        <v>30</v>
+      </c>
+      <c r="D12" s="69">
+        <v>1</v>
+      </c>
+      <c r="E12" s="69">
+        <v>2</v>
+      </c>
+      <c r="F12" s="69">
+        <v>3</v>
+      </c>
+      <c r="G12" s="69">
+        <v>4</v>
+      </c>
+      <c r="H12" s="69">
+        <v>5</v>
+      </c>
+      <c r="I12" s="15"/>
+      <c r="J12" s="75"/>
+      <c r="K12" s="69"/>
+      <c r="L12" s="69"/>
+      <c r="M12" s="74"/>
+      <c r="N12" s="15"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A13" s="15"/>
+      <c r="B13" s="69">
+        <v>6</v>
+      </c>
+      <c r="C13" s="69">
+        <v>7</v>
+      </c>
+      <c r="D13" s="69">
+        <v>8</v>
+      </c>
+      <c r="E13" s="69">
+        <v>9</v>
+      </c>
+      <c r="F13" s="69">
+        <v>10</v>
+      </c>
+      <c r="G13" s="69">
+        <v>11</v>
+      </c>
+      <c r="H13" s="69">
+        <v>12</v>
+      </c>
+      <c r="I13" s="15"/>
+      <c r="J13" s="75"/>
+      <c r="K13" s="69"/>
+      <c r="L13" s="69"/>
+      <c r="M13" s="74"/>
+      <c r="N13" s="15"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A14" s="15"/>
+      <c r="B14" s="69">
+        <v>13</v>
+      </c>
+      <c r="C14" s="69">
+        <v>14</v>
+      </c>
+      <c r="D14" s="69">
+        <v>15</v>
+      </c>
+      <c r="E14" s="69">
+        <v>16</v>
+      </c>
+      <c r="F14" s="69">
+        <v>17</v>
+      </c>
+      <c r="G14" s="69">
+        <v>18</v>
+      </c>
+      <c r="H14" s="69">
+        <v>19</v>
+      </c>
+      <c r="I14" s="15"/>
+      <c r="J14" s="75"/>
+      <c r="K14" s="69"/>
+      <c r="L14" s="69"/>
+      <c r="M14" s="74"/>
+      <c r="N14" s="15"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A15" s="15"/>
+      <c r="B15" s="69">
+        <v>20</v>
+      </c>
+      <c r="C15" s="69">
+        <v>21</v>
+      </c>
+      <c r="D15" s="69">
+        <v>22</v>
+      </c>
+      <c r="E15" s="69">
+        <v>23</v>
+      </c>
+      <c r="F15" s="69">
+        <v>24</v>
+      </c>
+      <c r="G15" s="69">
+        <v>25</v>
+      </c>
+      <c r="H15" s="69">
+        <v>26</v>
+      </c>
+      <c r="I15" s="15"/>
+      <c r="J15" s="75"/>
+      <c r="K15" s="69"/>
+      <c r="L15" s="69"/>
+      <c r="M15" s="74"/>
+      <c r="N15" s="15"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A16" s="15"/>
+      <c r="B16" s="69">
+        <v>27</v>
+      </c>
+      <c r="C16" s="69">
+        <v>28</v>
+      </c>
+      <c r="D16" s="69">
+        <v>29</v>
+      </c>
+      <c r="E16" s="69">
+        <v>30</v>
+      </c>
+      <c r="F16" s="69">
+        <v>31</v>
+      </c>
+      <c r="G16" s="69">
+        <v>1</v>
+      </c>
+      <c r="H16" s="69">
+        <v>2</v>
+      </c>
+      <c r="I16" s="15"/>
+      <c r="J16" s="75"/>
+      <c r="K16" s="69"/>
+      <c r="L16" s="69"/>
+      <c r="M16" s="74"/>
+      <c r="N16" s="15"/>
+    </row>
+    <row r="17" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="15"/>
+      <c r="B17" s="69">
+        <v>3</v>
+      </c>
+      <c r="C17" s="69">
+        <v>4</v>
+      </c>
+      <c r="D17" s="69">
+        <v>5</v>
+      </c>
+      <c r="E17" s="69">
+        <v>6</v>
+      </c>
+      <c r="F17" s="69">
+        <v>7</v>
+      </c>
+      <c r="G17" s="69">
+        <v>8</v>
+      </c>
+      <c r="H17" s="69">
+        <v>9</v>
+      </c>
+      <c r="I17" s="15"/>
+      <c r="J17" s="76"/>
+      <c r="K17" s="77"/>
+      <c r="L17" s="77"/>
+      <c r="M17" s="78"/>
+      <c r="N17" s="15"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A18" s="15"/>
+      <c r="B18" s="15"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="15"/>
+      <c r="H18" s="15"/>
+      <c r="I18" s="15"/>
+      <c r="J18" s="15"/>
+      <c r="K18" s="15"/>
+      <c r="L18" s="15"/>
+      <c r="M18" s="15"/>
+      <c r="N18" s="15"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A19" s="15"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="15"/>
+      <c r="H19" s="15"/>
+      <c r="I19" s="15"/>
+      <c r="J19" s="15"/>
+      <c r="K19" s="15"/>
+      <c r="L19" s="15"/>
+      <c r="M19" s="15"/>
+      <c r="N19" s="15"/>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A20" s="15"/>
+      <c r="B20" s="15"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="15"/>
+      <c r="I20" s="15"/>
+      <c r="J20" s="15"/>
+      <c r="K20" s="15"/>
+      <c r="L20" s="15"/>
+      <c r="M20" s="15"/>
+      <c r="N20" s="15"/>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="B21" s="15"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="15"/>
+      <c r="H21" s="15"/>
+      <c r="I21" s="15"/>
+      <c r="J21" s="15"/>
+      <c r="K21" s="15"/>
+      <c r="L21" s="15"/>
+      <c r="M21" s="15"/>
+      <c r="N21" s="15"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B3:H5"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBBD8683-FB9A-4469-813B-DEF57B3D6884}">
+  <dimension ref="A1:M17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="3" max="3" width="11" customWidth="1"/>
+    <col min="4" max="4" width="21.1796875" customWidth="1"/>
+    <col min="5" max="5" width="12.1796875" customWidth="1"/>
+    <col min="10" max="10" width="18.26953125" customWidth="1"/>
+    <col min="11" max="11" width="12.6328125" customWidth="1"/>
+    <col min="12" max="12" width="17.08984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D1" t="s">
+        <v>171</v>
+      </c>
+      <c r="E1" t="s">
+        <v>178</v>
+      </c>
+      <c r="I1" s="15"/>
+      <c r="J1" s="91" t="s">
+        <v>180</v>
+      </c>
+      <c r="K1" s="91"/>
+      <c r="L1" s="91"/>
+      <c r="M1" s="15"/>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="I2" s="15"/>
+      <c r="J2" s="64"/>
+      <c r="K2" s="15"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="I3" s="15"/>
+      <c r="J3" s="55" t="s">
+        <v>172</v>
+      </c>
+      <c r="K3" s="57"/>
+      <c r="L3" s="58"/>
+      <c r="M3" s="15"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="I4" s="15"/>
+      <c r="J4" s="55" t="s">
+        <v>173</v>
+      </c>
+      <c r="K4" s="57"/>
+      <c r="L4" s="58"/>
+      <c r="M4" s="15"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="I5" s="15"/>
+      <c r="J5" s="56" t="s">
+        <v>174</v>
+      </c>
+      <c r="K5" s="57"/>
+      <c r="L5" s="58"/>
+      <c r="M5" s="15"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="I6" s="15"/>
+      <c r="J6" s="56" t="s">
+        <v>175</v>
+      </c>
+      <c r="K6" s="57"/>
+      <c r="L6" s="58"/>
+      <c r="M6" s="15"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="I7" s="15"/>
+      <c r="J7" s="56" t="s">
+        <v>176</v>
+      </c>
+      <c r="K7" s="57"/>
+      <c r="L7" s="58"/>
+      <c r="M7" s="15"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="I8" s="15"/>
+      <c r="J8" s="62" t="s">
+        <v>177</v>
+      </c>
+      <c r="K8" s="63"/>
+      <c r="L8" s="63"/>
+      <c r="M8" s="15"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="I9" s="15"/>
+      <c r="J9" s="15"/>
+      <c r="K9" s="15"/>
+      <c r="L9" s="15"/>
+      <c r="M9" s="15"/>
+    </row>
+    <row r="10" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="I10" s="15"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="15"/>
+      <c r="L10" s="15"/>
+      <c r="M10" s="15"/>
+    </row>
+    <row r="11" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="I11" s="15"/>
+      <c r="J11" s="89" t="s">
+        <v>149</v>
+      </c>
+      <c r="K11" s="65"/>
+      <c r="L11" s="89" t="s">
+        <v>148</v>
+      </c>
+      <c r="M11" s="15"/>
+    </row>
+    <row r="12" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="I12" s="15"/>
+      <c r="J12" s="90"/>
+      <c r="K12" s="65"/>
+      <c r="L12" s="90"/>
+      <c r="M12" s="15"/>
+    </row>
+    <row r="13" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="I13" s="15"/>
+      <c r="J13" s="15"/>
+      <c r="K13" s="15"/>
+      <c r="L13" s="15"/>
+      <c r="M13" s="15"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="I14" s="15"/>
+      <c r="J14" s="89" t="s">
+        <v>181</v>
+      </c>
+      <c r="K14" s="15"/>
+      <c r="L14" s="89" t="s">
+        <v>182</v>
+      </c>
+      <c r="M14" s="15"/>
+    </row>
+    <row r="15" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="I15" s="15"/>
+      <c r="J15" s="90"/>
+      <c r="K15" s="15"/>
+      <c r="L15" s="90"/>
+      <c r="M15" s="15"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="I16" s="15"/>
+      <c r="J16" s="15"/>
+      <c r="K16" s="15"/>
+      <c r="L16" s="15"/>
+      <c r="M16" s="15"/>
+    </row>
+    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K17" s="15"/>
+      <c r="L17" s="15"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="J1:L1"/>
+    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="L14:L15"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF107AA7-8FB0-40A3-846B-77392F5D9BD7}">
   <dimension ref="A1:P42"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -3384,29 +4407,29 @@
     <col min="6" max="6" width="11.26953125" customWidth="1"/>
     <col min="7" max="7" width="18.1796875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="5.54296875" customWidth="1"/>
-    <col min="9" max="9" width="5.54296875" style="64" customWidth="1"/>
+    <col min="9" max="9" width="5.54296875" style="43" customWidth="1"/>
     <col min="10" max="10" width="6.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="64"/>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
-      <c r="H1" s="64"/>
-      <c r="J1" s="64"/>
-      <c r="K1" s="64"/>
-      <c r="L1" s="64"/>
-      <c r="M1" s="64"/>
-      <c r="N1" s="64"/>
-      <c r="O1" s="64"/>
-      <c r="P1" s="64"/>
+      <c r="A1" s="43"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="J1" s="43"/>
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
+      <c r="N1" s="43"/>
+      <c r="O1" s="43"/>
+      <c r="P1" s="43"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" s="64"/>
+      <c r="A2" s="43"/>
       <c r="B2" s="25"/>
       <c r="C2" s="26"/>
       <c r="D2" s="26"/>
@@ -3414,97 +4437,92 @@
       <c r="F2" s="26"/>
       <c r="G2" s="26"/>
       <c r="H2" s="27"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="64"/>
-      <c r="K2" s="64"/>
-      <c r="L2" s="64"/>
-      <c r="M2" s="64"/>
-      <c r="N2" s="64"/>
-      <c r="O2" s="64"/>
-      <c r="P2" s="64"/>
+      <c r="J2" s="43"/>
+      <c r="K2" s="43"/>
+      <c r="L2" s="43"/>
+      <c r="M2" s="43"/>
+      <c r="N2" s="43"/>
+      <c r="O2" s="43"/>
+      <c r="P2" s="43"/>
     </row>
     <row r="3" spans="1:16" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="64"/>
+      <c r="A3" s="43"/>
       <c r="B3" s="28"/>
-      <c r="C3" s="42" t="s">
+      <c r="C3" s="92" t="s">
         <v>142</v>
       </c>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
+      <c r="D3" s="92"/>
+      <c r="E3" s="92"/>
       <c r="F3" s="12"/>
       <c r="G3" s="12"/>
       <c r="H3" s="29"/>
-      <c r="I3" s="69"/>
-      <c r="J3" s="64"/>
-      <c r="K3" s="64"/>
-      <c r="L3" s="64"/>
-      <c r="M3" s="64"/>
-      <c r="N3" s="64"/>
-      <c r="O3" s="64"/>
-      <c r="P3" s="64"/>
+      <c r="J3" s="43"/>
+      <c r="K3" s="43"/>
+      <c r="L3" s="43"/>
+      <c r="M3" s="43"/>
+      <c r="N3" s="43"/>
+      <c r="O3" s="43"/>
+      <c r="P3" s="43"/>
     </row>
     <row r="4" spans="1:16" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="64"/>
+      <c r="A4" s="43"/>
       <c r="B4" s="28"/>
-      <c r="C4" s="43" t="s">
+      <c r="C4" s="93" t="s">
         <v>118</v>
       </c>
-      <c r="D4" s="43"/>
-      <c r="E4" s="43"/>
+      <c r="D4" s="93"/>
+      <c r="E4" s="93"/>
       <c r="F4" s="12"/>
       <c r="G4" s="12"/>
       <c r="H4" s="29"/>
-      <c r="I4" s="69"/>
-      <c r="J4" s="64"/>
-      <c r="K4" s="64"/>
-      <c r="L4" s="64"/>
-      <c r="M4" s="64"/>
-      <c r="N4" s="64"/>
-      <c r="O4" s="64"/>
-      <c r="P4" s="64"/>
+      <c r="J4" s="43"/>
+      <c r="K4" s="43"/>
+      <c r="L4" s="43"/>
+      <c r="M4" s="43"/>
+      <c r="N4" s="43"/>
+      <c r="O4" s="43"/>
+      <c r="P4" s="43"/>
     </row>
     <row r="5" spans="1:16" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="64"/>
+      <c r="A5" s="43"/>
       <c r="B5" s="28"/>
-      <c r="C5" s="44" t="s">
+      <c r="C5" s="94" t="s">
         <v>119</v>
       </c>
-      <c r="D5" s="44"/>
-      <c r="E5" s="44"/>
+      <c r="D5" s="94"/>
+      <c r="E5" s="94"/>
       <c r="F5" s="12"/>
       <c r="G5" s="13"/>
       <c r="H5" s="29"/>
-      <c r="I5" s="69"/>
-      <c r="J5" s="64"/>
-      <c r="K5" s="64"/>
-      <c r="L5" s="64"/>
-      <c r="M5" s="64"/>
-      <c r="N5" s="64"/>
-      <c r="O5" s="64"/>
-      <c r="P5" s="64"/>
+      <c r="J5" s="43"/>
+      <c r="K5" s="43"/>
+      <c r="L5" s="43"/>
+      <c r="M5" s="43"/>
+      <c r="N5" s="43"/>
+      <c r="O5" s="43"/>
+      <c r="P5" s="43"/>
     </row>
     <row r="6" spans="1:16" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="64"/>
+      <c r="A6" s="43"/>
       <c r="B6" s="28"/>
-      <c r="C6" s="44" t="s">
+      <c r="C6" s="94" t="s">
         <v>120</v>
       </c>
-      <c r="D6" s="44"/>
-      <c r="E6" s="44"/>
+      <c r="D6" s="94"/>
+      <c r="E6" s="94"/>
       <c r="F6" s="12"/>
       <c r="G6" s="13"/>
       <c r="H6" s="29"/>
-      <c r="I6" s="69"/>
-      <c r="J6" s="64"/>
-      <c r="K6" s="64"/>
-      <c r="L6" s="64"/>
-      <c r="M6" s="64"/>
-      <c r="N6" s="64"/>
-      <c r="O6" s="64"/>
-      <c r="P6" s="64"/>
+      <c r="J6" s="43"/>
+      <c r="K6" s="43"/>
+      <c r="L6" s="43"/>
+      <c r="M6" s="43"/>
+      <c r="N6" s="43"/>
+      <c r="O6" s="43"/>
+      <c r="P6" s="43"/>
     </row>
     <row r="7" spans="1:16" ht="15" x14ac:dyDescent="0.4">
-      <c r="A7" s="64"/>
+      <c r="A7" s="43"/>
       <c r="B7" s="28"/>
       <c r="C7" s="14"/>
       <c r="D7" s="14"/>
@@ -3512,17 +4530,16 @@
       <c r="F7" s="12"/>
       <c r="G7" s="13"/>
       <c r="H7" s="29"/>
-      <c r="I7" s="69"/>
-      <c r="J7" s="64"/>
-      <c r="K7" s="64"/>
-      <c r="L7" s="64"/>
-      <c r="M7" s="64"/>
-      <c r="N7" s="64"/>
-      <c r="O7" s="64"/>
-      <c r="P7" s="64"/>
+      <c r="J7" s="43"/>
+      <c r="K7" s="43"/>
+      <c r="L7" s="43"/>
+      <c r="M7" s="43"/>
+      <c r="N7" s="43"/>
+      <c r="O7" s="43"/>
+      <c r="P7" s="43"/>
     </row>
     <row r="8" spans="1:16" ht="16" x14ac:dyDescent="0.35">
-      <c r="A8" s="64"/>
+      <c r="A8" s="43"/>
       <c r="B8" s="28"/>
       <c r="C8" s="15"/>
       <c r="D8" s="15"/>
@@ -3534,17 +4551,16 @@
         <v>122</v>
       </c>
       <c r="H8" s="29"/>
-      <c r="I8" s="69"/>
-      <c r="J8" s="64"/>
-      <c r="K8" s="64"/>
-      <c r="L8" s="64"/>
-      <c r="M8" s="64"/>
-      <c r="N8" s="64"/>
-      <c r="O8" s="64"/>
-      <c r="P8" s="64"/>
+      <c r="J8" s="43"/>
+      <c r="K8" s="43"/>
+      <c r="L8" s="43"/>
+      <c r="M8" s="43"/>
+      <c r="N8" s="43"/>
+      <c r="O8" s="43"/>
+      <c r="P8" s="43"/>
     </row>
     <row r="9" spans="1:16" ht="16" x14ac:dyDescent="0.4">
-      <c r="A9" s="64"/>
+      <c r="A9" s="43"/>
       <c r="B9" s="28"/>
       <c r="C9" s="11"/>
       <c r="D9" s="14"/>
@@ -3552,17 +4568,16 @@
       <c r="F9" s="12"/>
       <c r="G9" s="13"/>
       <c r="H9" s="29"/>
-      <c r="I9" s="69"/>
-      <c r="J9" s="64"/>
-      <c r="K9" s="64"/>
-      <c r="L9" s="64"/>
-      <c r="M9" s="64"/>
-      <c r="N9" s="64"/>
-      <c r="O9" s="64"/>
-      <c r="P9" s="64"/>
+      <c r="J9" s="43"/>
+      <c r="K9" s="43"/>
+      <c r="L9" s="43"/>
+      <c r="M9" s="43"/>
+      <c r="N9" s="43"/>
+      <c r="O9" s="43"/>
+      <c r="P9" s="43"/>
     </row>
     <row r="10" spans="1:16" ht="16" x14ac:dyDescent="0.4">
-      <c r="A10" s="64"/>
+      <c r="A10" s="43"/>
       <c r="B10" s="28"/>
       <c r="C10" s="17" t="s">
         <v>123</v>
@@ -3579,17 +4594,16 @@
         <v>46228</v>
       </c>
       <c r="H10" s="29"/>
-      <c r="I10" s="69"/>
-      <c r="J10" s="64"/>
-      <c r="K10" s="64"/>
-      <c r="L10" s="64"/>
-      <c r="M10" s="64"/>
-      <c r="N10" s="64"/>
-      <c r="O10" s="64"/>
-      <c r="P10" s="64"/>
+      <c r="J10" s="43"/>
+      <c r="K10" s="43"/>
+      <c r="L10" s="43"/>
+      <c r="M10" s="43"/>
+      <c r="N10" s="43"/>
+      <c r="O10" s="43"/>
+      <c r="P10" s="43"/>
     </row>
     <row r="11" spans="1:16" ht="16" x14ac:dyDescent="0.35">
-      <c r="A11" s="64"/>
+      <c r="A11" s="43"/>
       <c r="B11" s="28"/>
       <c r="C11" s="17" t="s">
         <v>125</v>
@@ -3607,17 +4621,16 @@
         <v>0968273498</v>
       </c>
       <c r="H11" s="29"/>
-      <c r="I11" s="69"/>
-      <c r="J11" s="64"/>
-      <c r="K11" s="64"/>
-      <c r="L11" s="64"/>
-      <c r="M11" s="64"/>
-      <c r="N11" s="64"/>
-      <c r="O11" s="64"/>
-      <c r="P11" s="64"/>
+      <c r="J11" s="43"/>
+      <c r="K11" s="43"/>
+      <c r="L11" s="43"/>
+      <c r="M11" s="43"/>
+      <c r="N11" s="43"/>
+      <c r="O11" s="43"/>
+      <c r="P11" s="43"/>
     </row>
     <row r="12" spans="1:16" ht="16" x14ac:dyDescent="0.35">
-      <c r="A12" s="64"/>
+      <c r="A12" s="43"/>
       <c r="B12" s="28"/>
       <c r="C12" s="17" t="s">
         <v>127</v>
@@ -3635,17 +4648,16 @@
         <v>Flor de Bastion</v>
       </c>
       <c r="H12" s="29"/>
-      <c r="I12" s="69"/>
-      <c r="J12" s="64"/>
-      <c r="K12" s="64"/>
-      <c r="L12" s="64"/>
-      <c r="M12" s="64"/>
-      <c r="N12" s="64"/>
-      <c r="O12" s="64"/>
-      <c r="P12" s="64"/>
+      <c r="J12" s="43"/>
+      <c r="K12" s="43"/>
+      <c r="L12" s="43"/>
+      <c r="M12" s="43"/>
+      <c r="N12" s="43"/>
+      <c r="O12" s="43"/>
+      <c r="P12" s="43"/>
     </row>
     <row r="13" spans="1:16" ht="15" x14ac:dyDescent="0.4">
-      <c r="A13" s="64"/>
+      <c r="A13" s="43"/>
       <c r="B13" s="28"/>
       <c r="C13" s="15"/>
       <c r="D13" s="15"/>
@@ -3653,17 +4665,16 @@
       <c r="F13" s="13"/>
       <c r="G13" s="13"/>
       <c r="H13" s="29"/>
-      <c r="I13" s="69"/>
-      <c r="J13" s="64"/>
-      <c r="K13" s="64"/>
-      <c r="L13" s="64"/>
-      <c r="M13" s="64"/>
-      <c r="N13" s="64"/>
-      <c r="O13" s="64"/>
-      <c r="P13" s="64"/>
+      <c r="J13" s="43"/>
+      <c r="K13" s="43"/>
+      <c r="L13" s="43"/>
+      <c r="M13" s="43"/>
+      <c r="N13" s="43"/>
+      <c r="O13" s="43"/>
+      <c r="P13" s="43"/>
     </row>
     <row r="14" spans="1:16" ht="15" x14ac:dyDescent="0.4">
-      <c r="A14" s="64"/>
+      <c r="A14" s="43"/>
       <c r="B14" s="28"/>
       <c r="C14" s="13"/>
       <c r="D14" s="13"/>
@@ -3671,17 +4682,16 @@
       <c r="F14" s="13"/>
       <c r="G14" s="13"/>
       <c r="H14" s="29"/>
-      <c r="I14" s="69"/>
-      <c r="J14" s="64"/>
-      <c r="K14" s="64"/>
-      <c r="L14" s="64"/>
-      <c r="M14" s="64"/>
-      <c r="N14" s="64"/>
-      <c r="O14" s="64"/>
-      <c r="P14" s="64"/>
+      <c r="J14" s="43"/>
+      <c r="K14" s="43"/>
+      <c r="L14" s="43"/>
+      <c r="M14" s="43"/>
+      <c r="N14" s="43"/>
+      <c r="O14" s="43"/>
+      <c r="P14" s="43"/>
     </row>
     <row r="15" spans="1:16" ht="15" x14ac:dyDescent="0.4">
-      <c r="A15" s="64"/>
+      <c r="A15" s="43"/>
       <c r="B15" s="28"/>
       <c r="C15" s="33" t="s">
         <v>0</v>
@@ -3699,17 +4709,16 @@
         <v>132</v>
       </c>
       <c r="H15" s="29"/>
-      <c r="I15" s="69"/>
-      <c r="J15" s="64"/>
-      <c r="K15" s="64"/>
-      <c r="L15" s="64"/>
-      <c r="M15" s="64"/>
-      <c r="N15" s="64"/>
-      <c r="O15" s="64"/>
-      <c r="P15" s="64"/>
+      <c r="J15" s="43"/>
+      <c r="K15" s="43"/>
+      <c r="L15" s="43"/>
+      <c r="M15" s="43"/>
+      <c r="N15" s="43"/>
+      <c r="O15" s="43"/>
+      <c r="P15" s="43"/>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A16" s="64"/>
+      <c r="A16" s="43"/>
       <c r="B16" s="28"/>
       <c r="C16" s="35" t="s">
         <v>6</v>
@@ -3730,17 +4739,16 @@
         <v>30</v>
       </c>
       <c r="H16" s="29"/>
-      <c r="I16" s="69"/>
-      <c r="J16" s="64"/>
-      <c r="K16" s="64"/>
-      <c r="L16" s="64"/>
-      <c r="M16" s="64"/>
-      <c r="N16" s="64"/>
-      <c r="O16" s="64"/>
-      <c r="P16" s="64"/>
+      <c r="J16" s="43"/>
+      <c r="K16" s="43"/>
+      <c r="L16" s="43"/>
+      <c r="M16" s="43"/>
+      <c r="N16" s="43"/>
+      <c r="O16" s="43"/>
+      <c r="P16" s="43"/>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A17" s="64"/>
+      <c r="A17" s="43"/>
       <c r="B17" s="28"/>
       <c r="C17" s="36" t="s">
         <v>20</v>
@@ -3761,17 +4769,16 @@
         <v>30</v>
       </c>
       <c r="H17" s="29"/>
-      <c r="I17" s="69"/>
-      <c r="J17" s="64"/>
-      <c r="K17" s="64"/>
-      <c r="L17" s="64"/>
-      <c r="M17" s="64"/>
-      <c r="N17" s="64"/>
-      <c r="O17" s="64"/>
-      <c r="P17" s="64"/>
+      <c r="J17" s="43"/>
+      <c r="K17" s="43"/>
+      <c r="L17" s="43"/>
+      <c r="M17" s="43"/>
+      <c r="N17" s="43"/>
+      <c r="O17" s="43"/>
+      <c r="P17" s="43"/>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A18" s="64"/>
+      <c r="A18" s="43"/>
       <c r="B18" s="28"/>
       <c r="C18" s="36" t="s">
         <v>26</v>
@@ -3792,17 +4799,16 @@
         <v>60</v>
       </c>
       <c r="H18" s="29"/>
-      <c r="I18" s="69"/>
-      <c r="J18" s="64"/>
-      <c r="K18" s="64"/>
-      <c r="L18" s="64"/>
-      <c r="M18" s="64"/>
-      <c r="N18" s="64"/>
-      <c r="O18" s="64"/>
-      <c r="P18" s="64"/>
+      <c r="J18" s="43"/>
+      <c r="K18" s="43"/>
+      <c r="L18" s="43"/>
+      <c r="M18" s="43"/>
+      <c r="N18" s="43"/>
+      <c r="O18" s="43"/>
+      <c r="P18" s="43"/>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A19" s="64"/>
+      <c r="A19" s="43"/>
       <c r="B19" s="28"/>
       <c r="C19" s="21" t="s">
         <v>20</v>
@@ -3823,17 +4829,16 @@
         <v>60</v>
       </c>
       <c r="H19" s="29"/>
-      <c r="I19" s="69"/>
-      <c r="J19" s="64"/>
-      <c r="K19" s="64"/>
-      <c r="L19" s="64"/>
-      <c r="M19" s="64"/>
-      <c r="N19" s="64"/>
-      <c r="O19" s="64"/>
-      <c r="P19" s="64"/>
+      <c r="J19" s="43"/>
+      <c r="K19" s="43"/>
+      <c r="L19" s="43"/>
+      <c r="M19" s="43"/>
+      <c r="N19" s="43"/>
+      <c r="O19" s="43"/>
+      <c r="P19" s="43"/>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A20" s="64"/>
+      <c r="A20" s="43"/>
       <c r="B20" s="28"/>
       <c r="C20" s="21" t="s">
         <v>20</v>
@@ -3854,17 +4859,16 @@
         <v>30</v>
       </c>
       <c r="H20" s="29"/>
-      <c r="I20" s="69"/>
-      <c r="J20" s="64"/>
-      <c r="K20" s="64"/>
-      <c r="L20" s="64"/>
-      <c r="M20" s="64"/>
-      <c r="N20" s="64"/>
-      <c r="O20" s="64"/>
-      <c r="P20" s="64"/>
+      <c r="J20" s="43"/>
+      <c r="K20" s="43"/>
+      <c r="L20" s="43"/>
+      <c r="M20" s="43"/>
+      <c r="N20" s="43"/>
+      <c r="O20" s="43"/>
+      <c r="P20" s="43"/>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A21" s="64"/>
+      <c r="A21" s="43"/>
       <c r="B21" s="28"/>
       <c r="C21" s="21"/>
       <c r="D21" s="21" t="str">
@@ -3881,17 +4885,16 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="H21" s="29"/>
-      <c r="I21" s="69"/>
-      <c r="J21" s="64"/>
-      <c r="K21" s="64"/>
-      <c r="L21" s="64"/>
-      <c r="M21" s="64"/>
-      <c r="N21" s="64"/>
-      <c r="O21" s="64"/>
-      <c r="P21" s="64"/>
+      <c r="J21" s="43"/>
+      <c r="K21" s="43"/>
+      <c r="L21" s="43"/>
+      <c r="M21" s="43"/>
+      <c r="N21" s="43"/>
+      <c r="O21" s="43"/>
+      <c r="P21" s="43"/>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A22" s="64"/>
+      <c r="A22" s="43"/>
       <c r="B22" s="28"/>
       <c r="C22" s="21"/>
       <c r="D22" s="21" t="str">
@@ -3908,17 +4911,16 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="H22" s="29"/>
-      <c r="I22" s="69"/>
-      <c r="J22" s="64"/>
-      <c r="K22" s="64"/>
-      <c r="L22" s="64"/>
-      <c r="M22" s="64"/>
-      <c r="N22" s="64"/>
-      <c r="O22" s="64"/>
-      <c r="P22" s="64"/>
+      <c r="J22" s="43"/>
+      <c r="K22" s="43"/>
+      <c r="L22" s="43"/>
+      <c r="M22" s="43"/>
+      <c r="N22" s="43"/>
+      <c r="O22" s="43"/>
+      <c r="P22" s="43"/>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A23" s="64"/>
+      <c r="A23" s="43"/>
       <c r="B23" s="28"/>
       <c r="C23" s="21"/>
       <c r="D23" s="21" t="str">
@@ -3935,17 +4937,16 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="H23" s="29"/>
-      <c r="I23" s="69"/>
-      <c r="J23" s="64"/>
-      <c r="K23" s="64"/>
-      <c r="L23" s="64"/>
-      <c r="M23" s="64"/>
-      <c r="N23" s="64"/>
-      <c r="O23" s="64"/>
-      <c r="P23" s="64"/>
+      <c r="J23" s="43"/>
+      <c r="K23" s="43"/>
+      <c r="L23" s="43"/>
+      <c r="M23" s="43"/>
+      <c r="N23" s="43"/>
+      <c r="O23" s="43"/>
+      <c r="P23" s="43"/>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A24" s="64"/>
+      <c r="A24" s="43"/>
       <c r="B24" s="28"/>
       <c r="C24" s="21"/>
       <c r="D24" s="21" t="str">
@@ -3962,17 +4963,16 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="H24" s="29"/>
-      <c r="I24" s="69"/>
-      <c r="J24" s="64"/>
-      <c r="K24" s="64"/>
-      <c r="L24" s="64"/>
-      <c r="M24" s="64"/>
-      <c r="N24" s="64"/>
-      <c r="O24" s="64"/>
-      <c r="P24" s="64"/>
+      <c r="J24" s="43"/>
+      <c r="K24" s="43"/>
+      <c r="L24" s="43"/>
+      <c r="M24" s="43"/>
+      <c r="N24" s="43"/>
+      <c r="O24" s="43"/>
+      <c r="P24" s="43"/>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A25" s="64"/>
+      <c r="A25" s="43"/>
       <c r="B25" s="28"/>
       <c r="C25" s="21"/>
       <c r="D25" s="21" t="str">
@@ -3989,17 +4989,16 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="H25" s="29"/>
-      <c r="I25" s="69"/>
-      <c r="J25" s="64"/>
-      <c r="K25" s="64"/>
-      <c r="L25" s="64"/>
-      <c r="M25" s="64"/>
-      <c r="N25" s="64"/>
-      <c r="O25" s="64"/>
-      <c r="P25" s="64"/>
+      <c r="J25" s="43"/>
+      <c r="K25" s="43"/>
+      <c r="L25" s="43"/>
+      <c r="M25" s="43"/>
+      <c r="N25" s="43"/>
+      <c r="O25" s="43"/>
+      <c r="P25" s="43"/>
     </row>
     <row r="26" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="64"/>
+      <c r="A26" s="43"/>
       <c r="B26" s="28"/>
       <c r="C26" s="15"/>
       <c r="D26" s="15"/>
@@ -4007,17 +5006,16 @@
       <c r="F26" s="15"/>
       <c r="G26" s="15"/>
       <c r="H26" s="29"/>
-      <c r="I26" s="69"/>
-      <c r="J26" s="64"/>
-      <c r="K26" s="64"/>
-      <c r="L26" s="64"/>
-      <c r="M26" s="64"/>
-      <c r="N26" s="64"/>
-      <c r="O26" s="64"/>
-      <c r="P26" s="64"/>
+      <c r="J26" s="43"/>
+      <c r="K26" s="43"/>
+      <c r="L26" s="43"/>
+      <c r="M26" s="43"/>
+      <c r="N26" s="43"/>
+      <c r="O26" s="43"/>
+      <c r="P26" s="43"/>
     </row>
     <row r="27" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="64"/>
+      <c r="A27" s="43"/>
       <c r="B27" s="28"/>
       <c r="C27" s="15"/>
       <c r="D27" s="15"/>
@@ -4030,21 +5028,20 @@
         <v>210</v>
       </c>
       <c r="H27" s="29"/>
-      <c r="I27" s="69"/>
-      <c r="J27" s="77" t="s">
+      <c r="J27" s="53" t="s">
         <v>134</v>
       </c>
-      <c r="K27" s="78">
+      <c r="K27" s="54">
         <v>0.1</v>
       </c>
-      <c r="L27" s="64"/>
-      <c r="M27" s="64"/>
-      <c r="N27" s="64"/>
-      <c r="O27" s="64"/>
-      <c r="P27" s="64"/>
+      <c r="L27" s="43"/>
+      <c r="M27" s="43"/>
+      <c r="N27" s="43"/>
+      <c r="O27" s="43"/>
+      <c r="P27" s="43"/>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A28" s="64"/>
+      <c r="A28" s="43"/>
       <c r="B28" s="28"/>
       <c r="C28" s="15"/>
       <c r="D28" s="15"/>
@@ -4057,17 +5054,16 @@
         <v>31.5</v>
       </c>
       <c r="H28" s="29"/>
-      <c r="I28" s="69"/>
-      <c r="J28" s="64"/>
-      <c r="K28" s="64"/>
-      <c r="L28" s="64"/>
-      <c r="M28" s="64"/>
-      <c r="N28" s="64"/>
-      <c r="O28" s="64"/>
-      <c r="P28" s="64"/>
+      <c r="J28" s="43"/>
+      <c r="K28" s="43"/>
+      <c r="L28" s="43"/>
+      <c r="M28" s="43"/>
+      <c r="N28" s="43"/>
+      <c r="O28" s="43"/>
+      <c r="P28" s="43"/>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A29" s="64"/>
+      <c r="A29" s="43"/>
       <c r="B29" s="28"/>
       <c r="C29" s="15"/>
       <c r="D29" s="15"/>
@@ -4080,17 +5076,16 @@
         <v>21</v>
       </c>
       <c r="H29" s="29"/>
-      <c r="I29" s="69"/>
-      <c r="J29" s="64"/>
-      <c r="K29" s="64"/>
-      <c r="L29" s="64"/>
-      <c r="M29" s="64"/>
-      <c r="N29" s="64"/>
-      <c r="O29" s="64"/>
-      <c r="P29" s="64"/>
+      <c r="J29" s="43"/>
+      <c r="K29" s="43"/>
+      <c r="L29" s="43"/>
+      <c r="M29" s="43"/>
+      <c r="N29" s="43"/>
+      <c r="O29" s="43"/>
+      <c r="P29" s="43"/>
     </row>
     <row r="30" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="64"/>
+      <c r="A30" s="43"/>
       <c r="B30" s="28"/>
       <c r="C30" s="15"/>
       <c r="D30" s="15"/>
@@ -4103,17 +5098,16 @@
         <v>220.5</v>
       </c>
       <c r="H30" s="29"/>
-      <c r="I30" s="69"/>
-      <c r="J30" s="64"/>
-      <c r="K30" s="64"/>
-      <c r="L30" s="64"/>
-      <c r="M30" s="64"/>
-      <c r="N30" s="64"/>
-      <c r="O30" s="64"/>
-      <c r="P30" s="64"/>
+      <c r="J30" s="43"/>
+      <c r="K30" s="43"/>
+      <c r="L30" s="43"/>
+      <c r="M30" s="43"/>
+      <c r="N30" s="43"/>
+      <c r="O30" s="43"/>
+      <c r="P30" s="43"/>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A31" s="64"/>
+      <c r="A31" s="43"/>
       <c r="B31" s="28"/>
       <c r="C31" s="25" t="s">
         <v>138</v>
@@ -4123,17 +5117,16 @@
       <c r="F31" s="26"/>
       <c r="G31" s="27"/>
       <c r="H31" s="29"/>
-      <c r="I31" s="69"/>
-      <c r="J31" s="64"/>
-      <c r="K31" s="64"/>
-      <c r="L31" s="64"/>
-      <c r="M31" s="64"/>
-      <c r="N31" s="64"/>
-      <c r="O31" s="64"/>
-      <c r="P31" s="64"/>
+      <c r="J31" s="43"/>
+      <c r="K31" s="43"/>
+      <c r="L31" s="43"/>
+      <c r="M31" s="43"/>
+      <c r="N31" s="43"/>
+      <c r="O31" s="43"/>
+      <c r="P31" s="43"/>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A32" s="64"/>
+      <c r="A32" s="43"/>
       <c r="B32" s="28"/>
       <c r="C32" s="28"/>
       <c r="D32" s="15"/>
@@ -4141,17 +5134,16 @@
       <c r="F32" s="15"/>
       <c r="G32" s="29"/>
       <c r="H32" s="29"/>
-      <c r="I32" s="69"/>
-      <c r="J32" s="64"/>
-      <c r="K32" s="64"/>
-      <c r="L32" s="64"/>
-      <c r="M32" s="64"/>
-      <c r="N32" s="64"/>
-      <c r="O32" s="64"/>
-      <c r="P32" s="64"/>
+      <c r="J32" s="43"/>
+      <c r="K32" s="43"/>
+      <c r="L32" s="43"/>
+      <c r="M32" s="43"/>
+      <c r="N32" s="43"/>
+      <c r="O32" s="43"/>
+      <c r="P32" s="43"/>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A33" s="64"/>
+      <c r="A33" s="43"/>
       <c r="B33" s="28"/>
       <c r="C33" s="28"/>
       <c r="D33" s="15"/>
@@ -4159,17 +5151,16 @@
       <c r="F33" s="15"/>
       <c r="G33" s="29"/>
       <c r="H33" s="29"/>
-      <c r="I33" s="69"/>
-      <c r="J33" s="64"/>
-      <c r="K33" s="64"/>
-      <c r="L33" s="64"/>
-      <c r="M33" s="64"/>
-      <c r="N33" s="64"/>
-      <c r="O33" s="64"/>
-      <c r="P33" s="64"/>
+      <c r="J33" s="43"/>
+      <c r="K33" s="43"/>
+      <c r="L33" s="43"/>
+      <c r="M33" s="43"/>
+      <c r="N33" s="43"/>
+      <c r="O33" s="43"/>
+      <c r="P33" s="43"/>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A34" s="64"/>
+      <c r="A34" s="43"/>
       <c r="B34" s="28"/>
       <c r="C34" s="28" t="s">
         <v>139</v>
@@ -4179,17 +5170,16 @@
       <c r="F34" s="15"/>
       <c r="G34" s="29"/>
       <c r="H34" s="29"/>
-      <c r="I34" s="69"/>
-      <c r="J34" s="64"/>
-      <c r="K34" s="64"/>
-      <c r="L34" s="64"/>
-      <c r="M34" s="64"/>
-      <c r="N34" s="64"/>
-      <c r="O34" s="64"/>
-      <c r="P34" s="64"/>
+      <c r="J34" s="43"/>
+      <c r="K34" s="43"/>
+      <c r="L34" s="43"/>
+      <c r="M34" s="43"/>
+      <c r="N34" s="43"/>
+      <c r="O34" s="43"/>
+      <c r="P34" s="43"/>
     </row>
     <row r="35" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="64"/>
+      <c r="A35" s="43"/>
       <c r="B35" s="28"/>
       <c r="C35" s="30"/>
       <c r="D35" s="31"/>
@@ -4197,17 +5187,16 @@
       <c r="F35" s="31"/>
       <c r="G35" s="32"/>
       <c r="H35" s="29"/>
-      <c r="I35" s="69"/>
-      <c r="J35" s="64"/>
-      <c r="K35" s="64"/>
-      <c r="L35" s="64"/>
-      <c r="M35" s="64"/>
-      <c r="N35" s="64"/>
-      <c r="O35" s="64"/>
-      <c r="P35" s="64"/>
+      <c r="J35" s="43"/>
+      <c r="K35" s="43"/>
+      <c r="L35" s="43"/>
+      <c r="M35" s="43"/>
+      <c r="N35" s="43"/>
+      <c r="O35" s="43"/>
+      <c r="P35" s="43"/>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A36" s="64"/>
+      <c r="A36" s="43"/>
       <c r="B36" s="28"/>
       <c r="C36" s="15"/>
       <c r="D36" s="15"/>
@@ -4215,17 +5204,16 @@
       <c r="F36" s="15"/>
       <c r="G36" s="15"/>
       <c r="H36" s="29"/>
-      <c r="I36" s="69"/>
-      <c r="J36" s="64"/>
-      <c r="K36" s="64"/>
-      <c r="L36" s="64"/>
-      <c r="M36" s="64"/>
-      <c r="N36" s="64"/>
-      <c r="O36" s="64"/>
-      <c r="P36" s="64"/>
+      <c r="J36" s="43"/>
+      <c r="K36" s="43"/>
+      <c r="L36" s="43"/>
+      <c r="M36" s="43"/>
+      <c r="N36" s="43"/>
+      <c r="O36" s="43"/>
+      <c r="P36" s="43"/>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A37" s="64"/>
+      <c r="A37" s="43"/>
       <c r="B37" s="28"/>
       <c r="C37" s="15" t="s">
         <v>140</v>
@@ -4237,17 +5225,16 @@
       </c>
       <c r="G37" s="15"/>
       <c r="H37" s="29"/>
-      <c r="I37" s="69"/>
-      <c r="J37" s="64"/>
-      <c r="K37" s="64"/>
-      <c r="L37" s="64"/>
-      <c r="M37" s="64"/>
-      <c r="N37" s="64"/>
-      <c r="O37" s="64"/>
-      <c r="P37" s="64"/>
+      <c r="J37" s="43"/>
+      <c r="K37" s="43"/>
+      <c r="L37" s="43"/>
+      <c r="M37" s="43"/>
+      <c r="N37" s="43"/>
+      <c r="O37" s="43"/>
+      <c r="P37" s="43"/>
     </row>
     <row r="38" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="64"/>
+      <c r="A38" s="43"/>
       <c r="B38" s="30"/>
       <c r="C38" s="31"/>
       <c r="D38" s="31"/>
@@ -4255,82 +5242,81 @@
       <c r="F38" s="31"/>
       <c r="G38" s="31"/>
       <c r="H38" s="32"/>
-      <c r="I38" s="69"/>
-      <c r="J38" s="64"/>
-      <c r="K38" s="64"/>
-      <c r="L38" s="64"/>
-      <c r="M38" s="64"/>
-      <c r="N38" s="64"/>
-      <c r="O38" s="64"/>
-      <c r="P38" s="64"/>
+      <c r="J38" s="43"/>
+      <c r="K38" s="43"/>
+      <c r="L38" s="43"/>
+      <c r="M38" s="43"/>
+      <c r="N38" s="43"/>
+      <c r="O38" s="43"/>
+      <c r="P38" s="43"/>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A39" s="64"/>
-      <c r="B39" s="64"/>
-      <c r="C39" s="64"/>
-      <c r="D39" s="64"/>
-      <c r="E39" s="64"/>
-      <c r="F39" s="64"/>
-      <c r="G39" s="64"/>
-      <c r="H39" s="64"/>
-      <c r="J39" s="64"/>
-      <c r="K39" s="64"/>
-      <c r="L39" s="64"/>
-      <c r="M39" s="64"/>
-      <c r="N39" s="64"/>
-      <c r="O39" s="64"/>
-      <c r="P39" s="64"/>
+      <c r="A39" s="43"/>
+      <c r="B39" s="43"/>
+      <c r="C39" s="43"/>
+      <c r="D39" s="43"/>
+      <c r="E39" s="43"/>
+      <c r="F39" s="43"/>
+      <c r="G39" s="43"/>
+      <c r="H39" s="43"/>
+      <c r="J39" s="43"/>
+      <c r="K39" s="43"/>
+      <c r="L39" s="43"/>
+      <c r="M39" s="43"/>
+      <c r="N39" s="43"/>
+      <c r="O39" s="43"/>
+      <c r="P39" s="43"/>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A40" s="64"/>
-      <c r="B40" s="64"/>
-      <c r="C40" s="64"/>
-      <c r="D40" s="64"/>
-      <c r="E40" s="64"/>
-      <c r="F40" s="64"/>
-      <c r="G40" s="64"/>
-      <c r="H40" s="64"/>
-      <c r="J40" s="64"/>
-      <c r="K40" s="64"/>
-      <c r="L40" s="64"/>
-      <c r="M40" s="64"/>
-      <c r="N40" s="64"/>
-      <c r="O40" s="64"/>
-      <c r="P40" s="64"/>
+      <c r="A40" s="43"/>
+      <c r="B40" s="43"/>
+      <c r="C40" s="43"/>
+      <c r="D40" s="43"/>
+      <c r="E40" s="43"/>
+      <c r="F40" s="43"/>
+      <c r="G40" s="43"/>
+      <c r="H40" s="43"/>
+      <c r="J40" s="43"/>
+      <c r="K40" s="43"/>
+      <c r="L40" s="43"/>
+      <c r="M40" s="43"/>
+      <c r="N40" s="43"/>
+      <c r="O40" s="43"/>
+      <c r="P40" s="43"/>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A41" s="64"/>
-      <c r="B41" s="64"/>
-      <c r="C41" s="64"/>
-      <c r="D41" s="64"/>
-      <c r="E41" s="64"/>
-      <c r="F41" s="64"/>
-      <c r="G41" s="64"/>
-      <c r="H41" s="64"/>
-      <c r="J41" s="64"/>
-      <c r="K41" s="64"/>
-      <c r="L41" s="64"/>
-      <c r="M41" s="64"/>
-      <c r="N41" s="64"/>
-      <c r="O41" s="64"/>
-      <c r="P41" s="64"/>
+      <c r="A41" s="43"/>
+      <c r="B41" s="43"/>
+      <c r="C41" s="43"/>
+      <c r="D41" s="43"/>
+      <c r="E41" s="43"/>
+      <c r="F41" s="43"/>
+      <c r="G41" s="43"/>
+      <c r="H41" s="43"/>
+      <c r="J41" s="43"/>
+      <c r="K41" s="43"/>
+      <c r="L41" s="43"/>
+      <c r="M41" s="43"/>
+      <c r="N41" s="43"/>
+      <c r="O41" s="43"/>
+      <c r="P41" s="43"/>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A42" s="64"/>
-      <c r="B42" s="64"/>
-      <c r="C42" s="64"/>
-      <c r="D42" s="64"/>
-      <c r="E42" s="64"/>
-      <c r="F42" s="64"/>
-      <c r="G42" s="64"/>
-      <c r="H42" s="64"/>
-      <c r="J42" s="64"/>
-      <c r="K42" s="64"/>
-      <c r="L42" s="64"/>
-      <c r="M42" s="64"/>
-      <c r="N42" s="64"/>
-      <c r="O42" s="64"/>
-      <c r="P42" s="64"/>
+      <c r="A42" s="43"/>
+      <c r="B42" s="43"/>
+      <c r="C42" s="43"/>
+      <c r="D42" s="43"/>
+      <c r="E42" s="43"/>
+      <c r="F42" s="43"/>
+      <c r="G42" s="43"/>
+      <c r="H42" s="43"/>
+      <c r="J42" s="43"/>
+      <c r="K42" s="43"/>
+      <c r="L42" s="43"/>
+      <c r="M42" s="43"/>
+      <c r="N42" s="43"/>
+      <c r="O42" s="43"/>
+      <c r="P42" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -4347,9 +5333,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD2C011C-C52B-4DCE-A241-AAEDC6E1349C}">
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.1796875" bestFit="1" customWidth="1"/>
@@ -4361,16 +5347,21 @@
     <col min="10" max="10" width="15.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A1" s="41" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A1" s="95" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-    </row>
-    <row r="2" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
+      <c r="D1" s="95"/>
+      <c r="E1" s="95"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+    </row>
+    <row r="2" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
         <v>31</v>
       </c>
@@ -4386,11 +5377,13 @@
       <c r="E2" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="H2" s="46"/>
-      <c r="I2" s="46"/>
-      <c r="J2" s="46"/>
-    </row>
-    <row r="3" spans="1:10" ht="21" x14ac:dyDescent="0.5">
+      <c r="G2" s="66"/>
+      <c r="H2" s="96"/>
+      <c r="I2" s="96"/>
+      <c r="J2" s="96"/>
+      <c r="K2" s="66"/>
+    </row>
+    <row r="3" spans="1:11" ht="21" x14ac:dyDescent="0.5">
       <c r="A3" s="5" t="s">
         <v>36</v>
       </c>
@@ -4406,13 +5399,15 @@
       <c r="E3" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="H3" s="79" t="s">
+      <c r="G3" s="15"/>
+      <c r="H3" s="97" t="s">
         <v>147</v>
       </c>
-      <c r="I3" s="79"/>
-      <c r="J3" s="79"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I3" s="97"/>
+      <c r="J3" s="97"/>
+      <c r="K3" s="15"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>41</v>
       </c>
@@ -4428,9 +5423,13 @@
       <c r="E4" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="H4" s="45"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="G4" s="15"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="15"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
         <v>46</v>
       </c>
@@ -4446,13 +5445,15 @@
       <c r="E5" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="H5" s="80" t="s">
+      <c r="G5" s="15"/>
+      <c r="H5" s="55" t="s">
         <v>123</v>
       </c>
-      <c r="I5" s="82"/>
-      <c r="J5" s="83"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I5" s="57"/>
+      <c r="J5" s="58"/>
+      <c r="K5" s="15"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
         <v>51</v>
       </c>
@@ -4468,13 +5469,15 @@
       <c r="E6" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="H6" s="80" t="s">
+      <c r="G6" s="15"/>
+      <c r="H6" s="55" t="s">
         <v>143</v>
       </c>
-      <c r="I6" s="82"/>
-      <c r="J6" s="83"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I6" s="57"/>
+      <c r="J6" s="58"/>
+      <c r="K6" s="15"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
         <v>56</v>
       </c>
@@ -4490,13 +5493,15 @@
       <c r="E7" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="H7" s="81" t="s">
+      <c r="G7" s="15"/>
+      <c r="H7" s="56" t="s">
         <v>144</v>
       </c>
-      <c r="I7" s="82"/>
-      <c r="J7" s="83"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I7" s="57"/>
+      <c r="J7" s="58"/>
+      <c r="K7" s="15"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
         <v>61</v>
       </c>
@@ -4512,13 +5517,15 @@
       <c r="E8" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="H8" s="81" t="s">
+      <c r="G8" s="15"/>
+      <c r="H8" s="56" t="s">
         <v>145</v>
       </c>
-      <c r="I8" s="82"/>
-      <c r="J8" s="83"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I8" s="57"/>
+      <c r="J8" s="58"/>
+      <c r="K8" s="15"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
         <v>66</v>
       </c>
@@ -4534,13 +5541,15 @@
       <c r="E9" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="H9" s="81" t="s">
+      <c r="G9" s="15"/>
+      <c r="H9" s="56" t="s">
         <v>146</v>
       </c>
-      <c r="I9" s="82"/>
-      <c r="J9" s="83"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I9" s="57"/>
+      <c r="J9" s="58"/>
+      <c r="K9" s="15"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
         <v>71</v>
       </c>
@@ -4556,8 +5565,13 @@
       <c r="E10" s="6" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="15"/>
+    </row>
+    <row r="11" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="5" t="s">
         <v>76</v>
       </c>
@@ -4573,8 +5587,13 @@
       <c r="E11" s="6" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="G11" s="15"/>
+      <c r="H11" s="15"/>
+      <c r="I11" s="15"/>
+      <c r="J11" s="15"/>
+      <c r="K11" s="15"/>
+    </row>
+    <row r="12" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
         <v>81</v>
       </c>
@@ -4590,21 +5609,66 @@
       <c r="E12" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="H12" s="91" t="s">
+      <c r="G12" s="15"/>
+      <c r="H12" s="89" t="s">
         <v>149</v>
       </c>
-      <c r="I12" s="84"/>
-      <c r="J12" s="91" t="s">
+      <c r="I12" s="65"/>
+      <c r="J12" s="89" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="H13" s="92"/>
-      <c r="I13" s="84"/>
-      <c r="J13" s="92"/>
+      <c r="K12" s="15"/>
+    </row>
+    <row r="13" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="G13" s="15"/>
+      <c r="H13" s="90"/>
+      <c r="I13" s="65"/>
+      <c r="J13" s="90"/>
+      <c r="K13" s="15"/>
+    </row>
+    <row r="14" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="15"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="G15" s="15"/>
+      <c r="H15" s="89" t="s">
+        <v>181</v>
+      </c>
+      <c r="I15" s="15"/>
+      <c r="J15" s="89" t="s">
+        <v>182</v>
+      </c>
+      <c r="K15" s="15"/>
+    </row>
+    <row r="16" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="G16" s="15"/>
+      <c r="H16" s="90"/>
+      <c r="I16" s="15"/>
+      <c r="J16" s="90"/>
+      <c r="K16" s="15"/>
+    </row>
+    <row r="17" spans="7:11" x14ac:dyDescent="0.35">
+      <c r="G17" s="15"/>
+      <c r="H17" s="15"/>
+      <c r="I17" s="15"/>
+      <c r="J17" s="15"/>
+      <c r="K17" s="15"/>
+    </row>
+    <row r="18" spans="7:11" x14ac:dyDescent="0.35">
+      <c r="G18" s="15"/>
+      <c r="H18" s="15"/>
+      <c r="I18" s="15"/>
+      <c r="J18" s="15"/>
+      <c r="K18" s="15"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="7">
+    <mergeCell ref="H15:H16"/>
+    <mergeCell ref="J15:J16"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="H3:J3"/>
@@ -4630,9 +5694,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8127427E-8503-4A46-9B35-7016F7833F51}">
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.1796875" style="1" bestFit="1" customWidth="1"/>
@@ -4644,15 +5708,22 @@
     <col min="11" max="11" width="15.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A1" s="39" t="s">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A1" s="98" t="s">
         <v>86</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B1" s="98"/>
+      <c r="C1" s="98"/>
+      <c r="D1" s="98"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
         <v>87</v>
       </c>
@@ -4665,8 +5736,15 @@
       <c r="D2" s="7" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" ht="21" x14ac:dyDescent="0.5">
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+    </row>
+    <row r="3" spans="1:13" ht="21" x14ac:dyDescent="0.5">
       <c r="A3" s="1" t="s">
         <v>90</v>
       </c>
@@ -4679,14 +5757,17 @@
       <c r="D3" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="H3" s="85" t="s">
-        <v>147</v>
-      </c>
-      <c r="I3" s="85"/>
-      <c r="J3" s="85"/>
-      <c r="K3" s="85"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="G3" s="15"/>
+      <c r="H3" s="101" t="s">
+        <v>179</v>
+      </c>
+      <c r="I3" s="101"/>
+      <c r="J3" s="101"/>
+      <c r="K3" s="101"/>
+      <c r="L3" s="15"/>
+      <c r="M3" s="15"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>94</v>
       </c>
@@ -4699,9 +5780,15 @@
       <c r="D4" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="H4" s="45"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="G4" s="15"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="15"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>98</v>
       </c>
@@ -4714,14 +5801,17 @@
       <c r="D5" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="H5" s="86" t="s">
+      <c r="G5" s="15"/>
+      <c r="H5" s="59" t="s">
         <v>125</v>
       </c>
-      <c r="I5" s="47"/>
-      <c r="J5" s="88"/>
-      <c r="K5" s="48"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="I5" s="39"/>
+      <c r="J5" s="61"/>
+      <c r="K5" s="40"/>
+      <c r="L5" s="15"/>
+      <c r="M5" s="15"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>102</v>
       </c>
@@ -4734,14 +5824,17 @@
       <c r="D6" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="H6" s="87" t="s">
+      <c r="G6" s="15"/>
+      <c r="H6" s="60" t="s">
         <v>144</v>
       </c>
-      <c r="I6" s="47"/>
-      <c r="J6" s="88"/>
-      <c r="K6" s="48"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="I6" s="39"/>
+      <c r="J6" s="61"/>
+      <c r="K6" s="40"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="15"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>106</v>
       </c>
@@ -4754,14 +5847,17 @@
       <c r="D7" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="H7" s="87" t="s">
-        <v>155</v>
-      </c>
-      <c r="I7" s="47"/>
-      <c r="J7" s="88"/>
-      <c r="K7" s="48"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="G7" s="15"/>
+      <c r="H7" s="60" t="s">
+        <v>153</v>
+      </c>
+      <c r="I7" s="39"/>
+      <c r="J7" s="61"/>
+      <c r="K7" s="40"/>
+      <c r="L7" s="15"/>
+      <c r="M7" s="15"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>110</v>
       </c>
@@ -4774,14 +5870,17 @@
       <c r="D8" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="H8" s="87" t="s">
-        <v>156</v>
-      </c>
-      <c r="I8" s="47"/>
-      <c r="J8" s="88"/>
-      <c r="K8" s="48"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="G8" s="15"/>
+      <c r="H8" s="60" t="s">
+        <v>154</v>
+      </c>
+      <c r="I8" s="39"/>
+      <c r="J8" s="61"/>
+      <c r="K8" s="40"/>
+      <c r="L8" s="15"/>
+      <c r="M8" s="15"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>114</v>
       </c>
@@ -4794,30 +5893,98 @@
       <c r="D9" s="1" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="11" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="H11" s="89" t="s">
+      <c r="G9" s="15"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="15"/>
+      <c r="J9" s="15"/>
+      <c r="K9" s="15"/>
+      <c r="L9" s="15"/>
+      <c r="M9" s="15"/>
+    </row>
+    <row r="10" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="15"/>
+      <c r="L10" s="15"/>
+      <c r="M10" s="15"/>
+    </row>
+    <row r="11" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="G11" s="15"/>
+      <c r="H11" s="99" t="s">
         <v>149</v>
       </c>
-      <c r="I11" s="84"/>
-      <c r="J11" s="84"/>
-      <c r="K11" s="89" t="s">
+      <c r="I11" s="65"/>
+      <c r="J11" s="65"/>
+      <c r="K11" s="99" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="H12" s="90"/>
-      <c r="I12" s="84"/>
-      <c r="J12" s="84"/>
-      <c r="K12" s="90"/>
+      <c r="L11" s="15"/>
+      <c r="M11" s="15"/>
+    </row>
+    <row r="12" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="G12" s="15"/>
+      <c r="H12" s="100"/>
+      <c r="I12" s="65"/>
+      <c r="J12" s="65"/>
+      <c r="K12" s="100"/>
+      <c r="L12" s="15"/>
+      <c r="M12" s="15"/>
+    </row>
+    <row r="13" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="G13" s="15"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="15"/>
+      <c r="J13" s="15"/>
+      <c r="K13" s="15"/>
+      <c r="L13" s="15"/>
+      <c r="M13" s="15"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="G14" s="15"/>
+      <c r="H14" s="99" t="s">
+        <v>181</v>
+      </c>
+      <c r="I14" s="15"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="99" t="s">
+        <v>182</v>
+      </c>
+      <c r="L14" s="15"/>
+    </row>
+    <row r="15" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="G15" s="15"/>
+      <c r="H15" s="100"/>
+      <c r="I15" s="15"/>
+      <c r="J15" s="15"/>
+      <c r="K15" s="100"/>
+      <c r="L15" s="15"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="G16" s="15"/>
+      <c r="H16" s="15"/>
+      <c r="I16" s="15"/>
+      <c r="J16" s="15"/>
+      <c r="K16" s="15"/>
+      <c r="L16" s="15"/>
+    </row>
+    <row r="17" spans="7:12" x14ac:dyDescent="0.35">
+      <c r="G17" s="15"/>
+      <c r="H17" s="15"/>
+      <c r="I17" s="15"/>
+      <c r="J17" s="15"/>
+      <c r="K17" s="15"/>
+      <c r="L17" s="15"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="6">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="H11:H12"/>
     <mergeCell ref="K11:K12"/>
     <mergeCell ref="H3:K3"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="K14:K15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -4826,9 +5993,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{939D3273-81BC-4484-8AB7-D9A5E5AC22C2}">
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.1796875" bestFit="1" customWidth="1"/>
@@ -4840,16 +6007,22 @@
     <col min="12" max="12" width="9.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="40" t="s">
+    <row r="1" spans="1:13" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A1" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-    </row>
-    <row r="2" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B1" s="102"/>
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+    </row>
+    <row r="2" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -4865,14 +6038,16 @@
       <c r="E2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="49" t="s">
+      <c r="H2" s="66"/>
+      <c r="I2" s="103" t="s">
         <v>150</v>
       </c>
-      <c r="J2" s="49"/>
-      <c r="K2" s="49"/>
-      <c r="L2" s="49"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J2" s="103"/>
+      <c r="K2" s="103"/>
+      <c r="L2" s="103"/>
+      <c r="M2" s="66"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -4887,9 +6062,14 @@
         <v>10</v>
       </c>
       <c r="E3" s="3"/>
-      <c r="I3" s="45"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="H3" s="15"/>
+      <c r="I3" s="64"/>
+      <c r="J3" s="15"/>
+      <c r="K3" s="15"/>
+      <c r="L3" s="15"/>
+      <c r="M3" s="15"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -4904,14 +6084,16 @@
         <v>15</v>
       </c>
       <c r="E4" s="3"/>
-      <c r="I4" s="50" t="s">
+      <c r="H4" s="15"/>
+      <c r="I4" s="41" t="s">
         <v>151</v>
       </c>
-      <c r="J4" s="52"/>
-      <c r="K4" s="55"/>
-      <c r="L4" s="56"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J4" s="104"/>
+      <c r="K4" s="105"/>
+      <c r="L4" s="106"/>
+      <c r="M4" s="15"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
@@ -4926,14 +6108,16 @@
         <v>70</v>
       </c>
       <c r="E5" s="3"/>
-      <c r="I5" s="50" t="s">
+      <c r="H5" s="15"/>
+      <c r="I5" s="41" t="s">
         <v>152</v>
       </c>
-      <c r="J5" s="52"/>
-      <c r="K5" s="55"/>
-      <c r="L5" s="56"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J5" s="104"/>
+      <c r="K5" s="105"/>
+      <c r="L5" s="106"/>
+      <c r="M5" s="15"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
@@ -4948,14 +6132,16 @@
         <v>5</v>
       </c>
       <c r="E6" s="3"/>
-      <c r="I6" s="51" t="s">
+      <c r="H6" s="15"/>
+      <c r="I6" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="J6" s="52"/>
-      <c r="K6" s="55"/>
-      <c r="L6" s="56"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J6" s="104"/>
+      <c r="K6" s="105"/>
+      <c r="L6" s="106"/>
+      <c r="M6" s="15"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
@@ -4970,14 +6156,16 @@
         <v>100</v>
       </c>
       <c r="E7" s="3"/>
-      <c r="I7" s="51" t="s">
+      <c r="H7" s="15"/>
+      <c r="I7" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="J7" s="53"/>
-      <c r="K7" s="54"/>
-      <c r="L7" s="54"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J7" s="113"/>
+      <c r="K7" s="114"/>
+      <c r="L7" s="114"/>
+      <c r="M7" s="15"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>16</v>
       </c>
@@ -4992,14 +6180,16 @@
         <v>150</v>
       </c>
       <c r="E8" s="3"/>
-      <c r="I8" s="51" t="s">
+      <c r="H8" s="15"/>
+      <c r="I8" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="J8" s="52"/>
-      <c r="K8" s="55"/>
-      <c r="L8" s="56"/>
-    </row>
-    <row r="9" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="J8" s="104"/>
+      <c r="K8" s="105"/>
+      <c r="L8" s="106"/>
+      <c r="M8" s="15"/>
+    </row>
+    <row r="9" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
         <v>18</v>
       </c>
@@ -5014,8 +6204,14 @@
         <v>25</v>
       </c>
       <c r="E9" s="3"/>
-    </row>
-    <row r="10" spans="1:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H9" s="15"/>
+      <c r="I9" s="15"/>
+      <c r="J9" s="15"/>
+      <c r="K9" s="15"/>
+      <c r="L9" s="15"/>
+      <c r="M9" s="15"/>
+    </row>
+    <row r="10" spans="1:13" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>20</v>
       </c>
@@ -5030,16 +6226,18 @@
         <v>30</v>
       </c>
       <c r="E10" s="3"/>
-      <c r="I10" s="62" t="s">
-        <v>153</v>
-      </c>
-      <c r="J10" s="57"/>
-      <c r="K10" s="58" t="s">
-        <v>154</v>
-      </c>
-      <c r="L10" s="59"/>
-    </row>
-    <row r="11" spans="1:12" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="H10" s="15"/>
+      <c r="I10" s="107" t="s">
+        <v>149</v>
+      </c>
+      <c r="J10" s="67"/>
+      <c r="K10" s="109" t="s">
+        <v>148</v>
+      </c>
+      <c r="L10" s="110"/>
+      <c r="M10" s="15"/>
+    </row>
+    <row r="11" spans="1:13" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
         <v>22</v>
       </c>
@@ -5054,12 +6252,14 @@
         <v>45</v>
       </c>
       <c r="E11" s="3"/>
-      <c r="I11" s="63"/>
-      <c r="J11" s="57"/>
-      <c r="K11" s="60"/>
-      <c r="L11" s="61"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="H11" s="15"/>
+      <c r="I11" s="108"/>
+      <c r="J11" s="67"/>
+      <c r="K11" s="111"/>
+      <c r="L11" s="112"/>
+      <c r="M11" s="15"/>
+    </row>
+    <row r="12" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
         <v>24</v>
       </c>
@@ -5074,8 +6274,14 @@
         <v>25</v>
       </c>
       <c r="E12" s="3"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="H12" s="15"/>
+      <c r="I12" s="15"/>
+      <c r="J12" s="15"/>
+      <c r="K12" s="15"/>
+      <c r="L12" s="15"/>
+      <c r="M12" s="15"/>
+    </row>
+    <row r="13" spans="1:13" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>26</v>
       </c>
@@ -5090,8 +6296,18 @@
         <v>30</v>
       </c>
       <c r="E13" s="3"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="H13" s="15"/>
+      <c r="I13" s="107" t="s">
+        <v>181</v>
+      </c>
+      <c r="J13" s="15"/>
+      <c r="K13" s="109" t="s">
+        <v>182</v>
+      </c>
+      <c r="L13" s="110"/>
+      <c r="M13" s="15"/>
+    </row>
+    <row r="14" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
         <v>28</v>
       </c>
@@ -5106,18 +6322,36 @@
         <v>100</v>
       </c>
       <c r="E14" s="3"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="108"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="111"/>
+      <c r="L14" s="112"/>
+      <c r="M14" s="15"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="I15" s="15"/>
+      <c r="J15" s="15"/>
+      <c r="K15" s="15"/>
+      <c r="L15" s="15"/>
+      <c r="M15" s="15"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M16" s="15"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="11">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="I2:L2"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="K13:L14"/>
     <mergeCell ref="J6:L6"/>
     <mergeCell ref="J8:L8"/>
     <mergeCell ref="J7:L7"/>
     <mergeCell ref="I10:I11"/>
     <mergeCell ref="K10:L11"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="I2:L2"/>
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="J5:L5"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
